--- a/youtube_results.xlsx
+++ b/youtube_results.xlsx
@@ -473,96 +473,144 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>페이커 역대급 텔레포트, 결단 | LCK T1 vs GEN 스트리머 리액션 반응 모음</t>
+          <t>선픽이라도 캐리 하면 그만입니다 페이커의 요네! [Faker Stream Highlight]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Q4XAIc8DQe8</t>
+          <t>https://www.youtube.com/watch?v=kM5BbvXzRpA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ju1st</t>
+          <t>T1 Faker</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCHBzepJnvhFXCQDT4B181hg</t>
+          <t>https://www.youtube.com/channel/UCpJw2H9KKqwCCGQKRh1Bf2w</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>43090</t>
+          <t>534,609</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>12100</t>
+          <t>2,050,000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2025-09-01 00:00:00</t>
+          <t>2023-03-10 00:00:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>... but your computer or network may be sending automated queries. To protect our users, we can't process your request right now.</t>
+          <t>[음악]
+안녕하십니까 여러분
+뭐하지 올로 캐리어야 되지 도대체
+노성피케
+[음악]
+하고 캐리 해봐
+하나로 배구
+다른 하나로 봉인하리 이게 게요
+제대로 하겠습니다
+[음악]
+화이팅
+[음악]
+뭐야 이거
+바텀에도 죽어줬어 전설이다 전설 진짜
+게임
+[음악]
+이나 먹어도 좋은 판단이야
+라인 계획하지
+[음악]
+아니 너무 넘었어
+되나
+두 대만 칠게요 진짜로
+3인분 한 거 같은데요
+[음악]
+[음악]
+부나요
+아 이기적입니다 지금은
+눈도 먹고 두정도 먹고
+둘 다 먹을 수 있죠
+뭐죠 이거
+있으세요 빨리
+[음악]
+형님들
+합류해줘야겠다
+도망가버리기
+이번 판 젤리만 잡을게요 안 되겠다
+이거
+[음악]
+[음악]
+뭐야 이거 12%
+확률로 크기가 안 떴어 너 죽일
+뻔했네
+여기서 나오네
+나 자리만 죽인다
+[음악]
+초반 너무 불리해서
+여기까지 하겠습니다
+[음악]</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>예능 까지 진출한 페이커 게임 #T1 #도란#운타라</t>
+          <t>미친 페이커 근황</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=feVFCJRFxmU</t>
+          <t>https://www.youtube.com/watch?v=RAgxlHLHLyM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>롤피바라</t>
+          <t>이게맏나</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCykb57rMG7Y2mrKNsnXnnRg</t>
+          <t>https://www.youtube.com/channel/UCv2Lw7H0J_cdmW-ufy9UXwg</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>8,094,744</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>159,000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2025-09-05 00:00:00</t>
+          <t>2023-07-27 00:00:00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>... but your computer or network may be sending automated queries. To protect our users, we can't process your request right now.</t>
+          <t>능력 재력 모두 갖춘 페이커 어떻게
+지낼까요</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>그냥 누가 나 기절시켰다 깨워줘라 #t1 #페이커 #도란 #오너 #구마유시 #케리아 #lck #shorts</t>
+          <t>내 멘탈을 지키기 위한 쇼츠 #lck #t1 #페이커 #구마유시 #케리아 #오너 #도란 #shorts</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Q33wyTMyuBo</t>
+          <t>https://www.youtube.com/watch?v=AgMunMOmdy8</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -577,55 +625,80 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>57380</t>
+          <t>9,950</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>44300</t>
+          <t>45,300</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>2025-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>아직 정신 차리면 안 늦었다. 진짜
+아직 절대 안 늦었어. DK와 P어엑
+중 승자와 붙게 되는 티온. 사실 더
+말할 필요도 없이 이미 다들이 악물고
+준비하고 있을 거라 생각하 어차피
+패배를 했으니 이제 피드백만 자라면
+돼. 예방 주사라고 생각해야지 뭐.
+물론 지금 재앙의 경기력으로 남성
+호르몬이 작살나긴 했지만 그럼에도
+불구하고 진짜 작년보다 낫다. 위기가
+안 좋은 시기에 온 것뿐. 솔직히
+끝까지 봐야 한다고 생각하 당연히
+우리보다 훨씬 더 선수들이
+비상이겠지. 당장 남은 일정으로
+완벽한 새로운 플랜을 짜는 건 무리고
+지금 갖고 있는 승리 플랜을 다양한
+챔프로 날카롭게 깎아야 할 지금
+티원에게 직스는 유미 같은 거
+아닐까?이 이 정도로 처맞았으면
+벤카드 아깝다는 얘기는 난 나오지.
+어쨌든 먹고 죽어도 티원 팬이라는
+거.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3센치 텔드랍으로 아타칸 스틸하는 페이커를 본 스트리머 반응 모음ㅣT1 vs GEN | 08.30 | 2025 LCK</t>
+          <t>"아직 끝나지 않았습니다" 경기 후 쉬지 않고 바로 게임 돌리는 페이커 | 롤 하이라이트 LCK T1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=WjKRnQOCTTM</t>
+          <t>https://www.youtube.com/watch?v=ICaDK2gYBnI</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>롤 리더</t>
+          <t>T1덕후 티빠</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCN_NQvieqUqfq1gIQF1jzeA</t>
+          <t>https://www.youtube.com/channel/UCZE0CrbZaXylHJ36l_kXgSw</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>9589</t>
+          <t>4,994</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>24800</t>
+          <t>19,000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2025-08-30 00:00:00</t>
+          <t>2025-09-14 00:00:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -633,493 +706,2533 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>'지금도 이해가 안 가는' 페이커만 보는 각</t>
+          <t>크산테 그 긴거 #쇼메이커 #ShowMaker #shorts</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=D_gEpcc4Czw</t>
+          <t>https://www.youtube.com/watch?v=QpnZ2hO34os</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>롤따봉</t>
+          <t>Dplus KIA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCoo2pYADRxbV0q4LRrF4yNg</t>
+          <t>https://www.youtube.com/channel/UCepHesz_5Lwr7qRaqjB-p1A</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1133194</t>
+          <t>2,549,899</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9800</t>
+          <t>236,000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2025-07-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>2023-06-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>얘 아웃솔이지 이게
+아웃솔이야 이게
+끝이다
+이게 그 산타다
+인정 내가 졌다 내가 졌어 내가 졌어
+내가 졌어요
+체력 4,700 방어력 329 마저
+201인 챔피언이 저지불가 쉴드 벽
+넘기는 곳 있고요 에어본 있고
+심지어 쿨타임은 1초밖에 안 되고
+마나는 15 들고
+W 심지어 변신하면 쿨 초기화에다가
+패시브는 고정 피해가 들어가면
+방마저로 올리면 올릴수록 스킬 가속이
+생기고
+스킬 속도가 빨라지고 그 다음에
+공격력 개수가 있어 가지고
+w가</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>티젠전 페이커의 미친 아타칸스틸 서커스[T1 vs 젠지]</t>
+          <t>당시 엄청난 충격이었던 페이커의 조커픽, 미드 마스터이 사건</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5EMtEdKp4zQ</t>
+          <t>https://www.youtube.com/watch?v=vO5XBI0RTiA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>롤지직</t>
+          <t>롤사건사고누이</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UC8dc69U7w6_Uf9BccIx29Ag</t>
+          <t>https://www.youtube.com/channel/UCGt6h41qCj0i4WR6cYFYrvA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>308278</t>
+          <t>325,723</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>119,000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2025-08-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>2024-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>[음악]
+페이커 전설의 미드마이
+[음악]
+사건 사이에 글마 수도 있어
+아 형 자고 한번 해본 기고
+2015년 L 서머에서 SKT CJ
+엔투스가 만났을 때 생겼던
+[음악]
+사건입니다 안 떴으니까 오 참 다음에
+하자 아아 아지랑 근데 그것도 다
+카운터가 있어요 어
+알았서 근데 리드 알면은 진짜
+많 수 기 좋아요 마이 한번 해보던
+마이 야 근데 마이 해 그가 그렇게
+페이커는 CJ 투시를 상대로 미드
+마스터를 뽑았으며이 경기는 아직까지도
+회자되고 있습니다 거예요 아 오늘
+하면 안
+되겠다 오늘 솔로크 하지 마세요
+여러분 농 진단만 나왔던 하지 마세요
+진짜 코코더
+웃습니다 지원 됐으면 좀 아프죠
+SKT 시작부터 페이커를 키워 주려
+합니다 기 기죠 이거 조금만 앞으로
+나오면은 오리 마나까지 애까지 왜
+이거 마스터이 키에 먹인다 얘긴데요
+무조건 키 먹인다 아 이거 죽는
+각인데요 죽는 각이에요 죽는 먹어 케
+먹어
+아 어쉬 어쉬 괜찮아 모든 먹어 모든
+먹어 그고 눌러 그리고 이런 상황에서
+라인이 또 좋은 라인도 아니고 지금
+상당히 피곤해요 최악의 라인이죠 이게
+정글의 어 정글의 기수 없습니다 났어
+이거 완전 게임집니다 미션까지
+잘리면서 SKT 초반 흐름을
+가져갑니다 SKT 다시 한번 코코를
+노리요 좀 그만 돼 버려도 어 킬 아
+그래 예 뱅기는 죽었습니다 이거는
+뭔가 어 어 어 또차 어디까지 끝까지
+주네 넌 이미 죽어 있다 거기다
+엠비션 그지 다시 잘리면서 CJ n
+초반부터 완전 말리게 됩니다 게임이
+이건 진짜 거의 예 반쯤 터진
+느낌이에요 완 이번엔 마린과 뱅기가
+바텀에 있는 샤이를
+노립니다 자 그래도 2세트 전승이라는
+거는 시가 멘탈이 강하다는 이 긴
+통로 뚫려요 럼블 전멸 없습니다네 긴
+통로 뚫려요 저 럼블 다로
+위로
+이런식으로
+마을
+[박수]
+2대 아 사이만 만나면 예 말렸던
+시제는 샤이가 더블 킬을 하면서
+흐름을 바꿔 나갔습니다 예 변기까지
+같이 갔어 이거 시제이 완전 무너지고
+있는
+단계였는데 진짜 희망의 불씨가 일단
+솟아 올랐 이번엔 엠비션이 페이코를
+노립니다 자 이제 앰비션이 자 여기
+한번더 창 꺾고 창 맞춰두고 한번 더
+한번더 한번더
+잡았어요
+스죠 그럼 탔습니다 cjn 페이코를
+잡아내며 스코어를 따라잡았지만 나가고
+있네 이제는 저기 지금 탑에 올라가
+있는 저 바텀 라인만면 되는데 어 자
+어네
+오 데미지 데미지
+데미지가
+고린 마린 생전네 회복 써주면서
+그죠 사실 CJ 지금 이렇게 다 모인
+김에 모르가나 송마리 동도 없고 탑에
+있으니까 어 자 없 상이 맞았어요
+까지 코코를 두 번 연속 잘라내면서
+SKT 다시 흐름을 잡기 시작합니다
+이번에도 마린이 코코를 잡자면 핑을
+찍었습니다이 타이밍에 꽤 강한
+조합이었다 보리가 그렇죠 SKT
+입장에선 글고 앞서 있고 미드 포탄
+먼저 밀었고 이런 거면 충분합니다 어
+선동데 또 거리가 있긴 있거든요 아
+그럴땐 달리가 보고 있어요 그 격
+당겨 마이가 마이가
+마이가고 하
+아어요 그러나 이거 잡아 잡 만약
+모르가나가 잡혔다면 입장에서 아 그래
+이건 우리가 그래도 2대이야 괜찮아
+할 수 있지만 모르가나가 사랑한
+시점에서이 때문 그죠 마리는 살리면서
+두 명 그 칼로 긋고 본인이
+죽었으니까 점프 띄어서 데미지
+들어오는 타이밍에 전멸 기가막혀
+했었거든요 예 모두가 하나만 죽을
+뻔한 걸 2대 1로 바꿔줬습니다 용이
+나올 타이밍에 cjn 교전을 준비하고
+있습니다 그때 마린이 디트를
+사용하면서 오히려 CJ 기습 당합니다
+그 좋지 않아요 물론 쓸어담는 경우
+있죠에 뒤에
+모르가나 기습을 먼저 당했어요
+세상에 자
+보세 어 위치전환
+그에 무자비한 카이이 시작되고 있어요
+그리고 갈리스도 아 네명
+전 발론 발론 되겠죠 발이죠네 그렇게
+바론까지 먹히면서 다시 차이가
+벌어졌고
+기회를 노리던 CJ 코코가 궁으로기를
+노리면서 한타로 이어집니다 이러면 자
+기기를 아이고 기는 살아가나요 기
+한방 한방 기 자
+미 여기 안
+와도지 전 마스 마스터 빨 야 마스터
+와요 마스터 와요
+스라어요 켰어요
+버립니다 또 에이스
+더블킬까지
+와 그냥 밀어붙 이건 뭐
+억제기
+기본
+와 잠깐만요 게임 끝 예 설마 하나
+더 괴 가능하겠는데요 상대는 천히
+너무 빨리 깨지는데 11가 아무리
+저항을 해도 지금 나오자마자 만피
+나오자마자 만피 과연
+이대 잡아 한대 약간 시간이 끌리는
+미드를 사인을 하는데
+뭐해
+명죠 빨라요 그리고 바텀에서 바텀에서
+니달리가
+죽었습니다 아 마이 사랑합니다 자
+그러면 이쪽 이쪽
+버텨야죠 그 참 결국 란 건 상황에
+따라 돌고 도는 거고 결과를 보고이
+해을 할 수밖 없는 분이 있는 건 맞
+그런 점에서 니달리가 진짜 어떻게
+할게 없어졌네요 이게 조합이 포킹
+조합도 아니고 아 한방이 거 아
+뱅이가
+죽는 죽어도 되고요 마이 탑에
+있습니다 집에 안 갔어요 지금
+모르가나는거든요 데미지가 살벌해 지금
+여기 탑에서도 지금 아우 성이에요
+지금 자 혼자 깬다 자 이거 혹시
+1대일 그냥 잡아버리는 거 아닌가요
+어떤 비전 이달리 자 그러면 이거
+쌍둥이 쌍둥이 이거 이거 뭐 그냥
+들어가면 들어가면요 와네 자
+모르가나가 실도 차고 실드
+차고네 대이 내 거야네 끝 내겠는데
+끝났습니다 1점 앞에다 마린이
+가이드라인
+제제 결국 SKT
+승리합니다 드라마틱하게 이겨야 한다
+팬들께 큰 즐거움을 안겨 드리자 야
+SK 텔레콤이기는 것도 중요합니다
+거기에 또 이런 팬서비스 그리고 뭔가
+한 단계 뭔가 플 바라보는 그런 그
+시야까지 있는 거 아니에요 그렇습니다
+아 역시 뭐 많은 팬분들이 좋아하시는
+것 공격적인 플레이 공격적인 픽으로
+화끈한 스리를 거두는 것 아니겠습니까
+SK 텔콤 티원은 그것도 충분히
+만족시켜주는 경기력을 이번 서머 시즌
+내내 보여주고 있는데 이렇게
+중간중간에 페이커라는 정말 우주
+데스를 중심으로 계속 픽을 보여주면서
+픽 이렇게 완승을 거니다 그렇습니다네
+경기 종료후 MVP 선수로 선정됐던
+페이커의 인터뷰입니다 SK 텔레콤
+원이었습니다 정말 강했죠 여러분 박수
+부탁드립니다 지금바로 페이커 선수
+단독 인터뷰 해보도록 하겠습니다
+축하드립니다 페이커 선수 정말 오늘
+두말할 것 없이 완벽 캐리 하셨는데요
+승리소감 어떠신가요 오늘 CJ 워낙
+강력한 팀이라서 좀 많이 걱정을 하고
+왔는데 좀 어 저희가 경기력이
+이전보다 좀 더 잘 나온 거 같아서
+좀 족스 네 그리고 미드 마이에 대해
+질문했습니다 뭐 제가 마이 같은
+경우에는 좀 어 좀 한다는 소문이
+있어서 뭐 그렇게 당황하지 않았을 것
+같은데 그래도 뭐 먼저 제가 미드도
+안 나는데 뽑았기 때문에 좀 막 어
+뭐라고 했을 수도 있을 것
+같아요네 페이커 선수도 그렇고 저도
+그렇고 아마 많은 팬분들이 오프다들을
+궁금해하실 거 같은데요 자 말나온
+김에 이세트 마스터이 이야기를 좀
+해보도록
+하겠습니다이트 마스터이를 픽하기 전에
+모르가나와 애니를
+픽했던 조합이었어요
+어 제가 마스터를 좀 준비하면서 어
+그게 그 애니와 모르가나가 좀 잘
+맞는 챔피언이라고 좀 생각을 했어요네
+그래서 좀 어 마스터이를 픽하기 좀
+좋은 상황이었던 거 같고 또 상대
+조합 자체도 좀 어 마스터가 좀
+활약하게 좋은 조합이다 보니까
+선택했던 거 같아요 영상을
+시청해주셔서 정말 감사합니다
+[음악]</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>소름 돋는 페이커 우승 서사 ㄷㄷ</t>
+          <t>2029년까지 전설을 써내려 갈 ✨페이커✨ 대상혁의 재계약을 진심으로 축하합니다 #유퀴즈</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=CxLzOKJCQWU</t>
+          <t>https://www.youtube.com/watch?v=6RUnvBH34aU</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>숏밍아웃</t>
+          <t>디글 클래식 :Diggle Classic</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCuTMqcP_waXNHXS6bxanTYQ</t>
+          <t>https://www.youtube.com/channel/UCRMA_Nb5VF-YoWApSVeXPVA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12945933</t>
+          <t>202,194</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>57600</t>
+          <t>3,150,000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2024-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>2025-07-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>올해 리그 오브 레전드 그 월드
+챔피언십 일명 그 롤드컵이 이게 누적
+시청자 수가 4억명
+&gt;&gt; 야
+&gt;&gt; 이거 동시 접속자 수가 결승에 1억명
+예 그리고 이제 고척 스카이도
+1천녀석이
+10분 만에 매진이 됐고요. 그리고
+이제 광화문에도 그날 날이 추웠어요.
+근데 한 15,여명 분 정도의
+&gt;&gt; 길거리 응원이
+&gt;&gt; 길거리 응원이 이루어지고
+&gt;&gt; 와이
+&gt;&gt; 말 그대로 역대급 관심이 좀
+쏟아졌습니다. 특히 뜨거웠던 경기가
+이제 중결승전과 결승전 요게 좀
+굉장히 좀 뜨겁는데 중국 팀이었죠.
+징동팀. 예.요 팀과의 대결이 사실상
+결승적이었다. 요런 얘기가 좀
+있더라고요.
+&gt;&gt; 네.
+진동이 이제 한해 있는 대회를 다
+우승해 가지고
+&gt;&gt; 아이 팀이 되게 강 팀이라
+그러더라고요. 예. 네. 이제
+2023년도에 그 중국팀이니까 중국
+자국 리그 다 우승하고
+&gt;&gt; 그리고 이제 MSI라고 이제 월즈보다
+조금 작은 중간 대회가 있는데
+&gt;&gt; 그건 국제 대회거든요. 그때 이제네
+&gt;&gt; 막 붙었었는데 저희랑도
+&gt;&gt; 음
+&gt;&gt; 그때 또 진동에 우승해 가지고
+&gt;&gt; 아
+&gt;&gt; 좀 사실 이번 월즈에서 저도 진동이랑
+이제 만나는 거를 되게 기다리고
+있었거든요. 네. 시작할 때부터
+&gt;&gt; 이제 진동이 너무 잘하는 팀이니까
+빨리 맛붙고 경기하고 싶다 이런
+생각이 들었는데
+&gt;&gt; 네
+&gt;&gt; 저희가 3대 1로 이겨 가지고
+선수들도 다 기뻐하고야네
+&gt;&gt; 엄청 좋아했습니다. 2015 2016
+그리고 올해까지 롤드컵 통산 4회
+우승 와 롤드컵 최다 우승자인 동시에
+역대 최연소 그리고 최고령 우승 와
+이게 전무 후무한 기록이에요 정말
+이게 나이가 이제 아직도 20대신데
+벌써 이쪽에서는 지금
+&gt;&gt; 최령
+&gt;&gt; 아 벌써 그렇습니까?
+&gt;&gt; 그러게요. 네. 어, 일단은 제가
+27인데만으로
+27인데
+&gt;&gt; 근데 게이머들이 보통 20대
+초중반이니까
+&gt;&gt; 아,
+&gt;&gt; 네. 바둑 같은 것도 사실은 되게
+마인드 스포츠잖아요.
+&gt;&gt; 근데 바둑도이 스포츠랑 비슷하게 거의
+10대 후반부터 그때가 전성기라서
+게임도 아마 그때가 전성기지 않나
+생각해요.맞죠.
+&gt;&gt; 음. 이게 이제 아마이 대회를
+준비하면서 진짜 엄청나게 훈련을
+하시지 않았을까요?
+&gt;&gt; 네. 거의 이제 24시간을 이제 게임
+연습하는 목적의 생활만 하고 있죠.
+그냥 먹고 자고 운동도 조금 하고
+&gt;&gt; 네. 새벽 한 세 4시까지 하고
+&gt;&gt; 네. 그렇게 하고 있습니다.
+&gt;&gt; 그 일명 이제 제오페 국회 예. 우리
+팀원들이죠.
+&gt;&gt; 제오스, 오너, 구마유시, 캐리아.
+예. 이렇게 이제 팀원 팀원 분들인데
+다 같이 정말 고생 많으셨잖아요.
+박수로 한번 좀. 예. 진짜 고생
+많으셨습니다. 예.
+이게 저 사실 페이커 선수가 이번
+우승은 이제 내가 아닌 팀을 위한
+우승이다. 특히 좀 이런 생각이 올해
+또 좀 강했던 이유가 좀 있을까요?
+&gt;&gt; 제 좀 오래 들어서 제가 목표가 조금
+있어야겠다라는 생각을 했어요. 이제
+사실 저는 벌었을 때 처음 대비했을
+때는 좀 돈을 많이 벌고 싶었어요.
+&gt;&gt; 어 그럴 수 있죠. 그렇죠.
+그렇죠.대
+많대
+준비 열심히 하고 아 우승에서 상금
+버려야겠다 이런 생각이었는데
+&gt;&gt; 해가 지나면 지날수록 이제 돈이라는
+그런 목표를 많이 달성을 했으니까 또
+다른 새로운 목표가 있어야 되잖아요.
+동기 부여를 하려면. 음. 그러면은
+이제 뭐가 중요하지라고 생각을 했을
+때 저는 명예가 중요하다고
+생각했어요. 그다음에는 그래서
+&gt;&gt; 많이 우승하고 또 많은 사람들에게 아
+내가 대단한 걸 좀 알려야겠다 그렇게
+생각을 해서
+&gt;&gt; 명예를 택했는데 이제 나중에는 제가
+&gt;&gt; 커가 많이 쌓였어요. 음. 그래서
+이제 무슨 목표를 또 세워야 되나
+그렇게 생각을 많이 했습니다.
+&gt;&gt; 아 그래서 아 그래서이 우승이 예
+&gt;&gt; 그래서네 어떤 목표가 좋을까
+생각하다가 이제 좀 저 스스로보다는
+다른 사람을 위한 목표가 있으면은
+계속해서 내가
+&gt;&gt; 그 목표를 계속 따라갈 수 있겠구나
+그럴 생각했습니다.
+&gt;&gt; 야 이게 뭐 이제 진짜 어 사실
+&gt;&gt; 올해 나이가 이제 페이커가 27세
+아닙니까?
+근데
+&gt;&gt; 근데 이제 돈도 목표가 아니고
+&gt;&gt; 이거잖아요. 그까 사실은
+&gt;&gt; 멋있다.
+&gt;&gt; 예.
+&gt;&gt; 아 멋있다.
+&gt;&gt; 뭐 그 많이 보셨죠?
+&gt;&gt; 아 이게 이제 요런 얘기를 좀
+드릴게요. 뭐 이어사이가 그런데 이게
+이제 페이커가 이제 중국에서 240억
+이적제이가
+이게 들어왔는데
+&gt;&gt; 이거 팀에 남기 위해서 요거를 이제
+거절을 하신 거예요? 어, 일단 뭐
+저는 여러 가지 조건을 이제 다
+보고긴 하는데 그래도 아무래도 제
+목표가 돈이나 그런 명예 그런
+것보다는 좀 더 배우고 성장하는 거에
+조금 더 초점을 많이 뒀어요.
+최근에는. 그래서 그리고 뭐 저희
+이제 팀에서도 많은 좋은 대우를 해
+주니까요.
+&gt;&gt; 남았던 거 같습니다. 아, 물론 이제
+팀에서도 좋은 대우를 하긴 하겠지만
+이게 사실 막상 내가 아무리 마음을
+굳건히 먹어도 240억.
+&gt;&gt; 그럼 이제 주변에서는 야, 그
+240억인데 그걸 왜 안 가? 이러면
+&gt;&gt; 그 주변 가족분들이라든가
+&gt;&gt; 네. 저희 가족분들은 제 선택을 또
+많이
+&gt;&gt; 존중을 해주시.
+&gt;&gt; 네. 존중해고
+&gt;&gt; 뭐 근데 이게 약간 금액기나 그런게
+좀 차이가 있을 수도 있기는 해요.
+알려진 거랑. 그래서
+&gt;&gt; 뭐 이게 딱 240억은 아니다. 예.
+어쨌든
+&gt;&gt; 아니 오늘 링가 어저께가 봤는데 기사
+봤는데 다들 전원 재계약하셨다고.
+네. 맞아요.
+&gt;&gt; 아유 이거 참 또
+&gt;&gt; 뭐 이게 참 뭐 여러모로 또 팀원들
+간의 참 이런 생각과 마음이
+맞는다라는게 또 쉽지 않아요. 아
+그리고 또 각자의 선택이잖아요. 예.
+팀도 팀이지만.
+&gt;&gt; 예. 예. 집에도 이제 가끔 팀원들을
+좀 초대하는데 음
+&gt;&gt; 어 집이 궁전이라는 소리가
+&gt;&gt; 한간에 좀 있어요. 페이커의 집이
+궁전이다. 이거 한번 오늘 확인해
+봅니다. 네. 솔직하게 좀 얘기를 해
+주세요. 페이커.
+&gt;&gt; 네. 군전 아니고 집이고요.
+&gt;&gt; 예.
+&gt;&gt; 네. 집이고. 아, 왜냐면 팀원들이
+페이커의 집에 초대를 받아서 갔다 온
+목욕담이에요.
+&gt;&gt; 안녕하세요. 저는 티원의 구현시
+이민영입니다.
+어, 안에 제가 완벽히 다 둘러보진
+않았지만 너무 커 가지고
+확실히 좀 평범한 집은 아닌 거 같은
+그런 느낌이었습니다.
+그냥 방도 되게 많고 그냥 되게 컸던
+거 같고 많은 사람들이 살 수 있겠다
+생각했습니다.
+&gt;&gt; 확실히 컨텐츠가 되게 많더라고요.
+집에 이것저것 할 수 있는 것들이
+너무 마음에 들어서 저는 거기서 계속
+그냥 지했었던 거 같아요.
+지하가 본 곳은 지하 한 군데밖에
+아니어서
+거기가 저의 본가보다 좀 큰 거
+같아서
+&gt;&gt; 또 이제 MS 이제 많이 뿌려 가지고
+&gt;&gt; 그러니까 그걸 좀 잡아 주세요.
+&gt;&gt; 네.
+&gt;&gt; 어 일단 집이 너무 커서 순레 잡기
+해도 된다.
+&gt;&gt; 아 뭐
+&gt;&gt; 그건 어때요? 아, 근데 집이 조금
+크긴 합니다.
+&gt;&gt; 그러니까 저희 아버지가 건축 쪽을
+잘하셔 가지고
+&gt;&gt; 아,
+&gt;&gt; 직접 좀 다 하셔 가지고
+&gt;&gt; 설계를 좀 하셨어요.
+&gt;&gt; 어,
+&gt;&gt; 그래가지고 그니까 첫 번째이 질문
+순례잡기 해도 된다.
+&gt;&gt; 되긴 되긴 했 되긴 했던 거 같아.
+술 첫 번째 목격은 되긴 된다.
+&gt;&gt; 만 먹으면 할 수 있다.
+&gt;&gt; 만 먹으면 할 수 있다.
+&gt;&gt; 뭐 완벽하게 뭐 순례 자기를 어느
+정도 사이즈를 원하는지 모르지만 뭐
+되긴 된다. 못 할 건 없다.
+&gt;&gt; 자, 두 번째 얘기입니다. 지하의
+커다란 동굴 같은 곳이 있는데
+영화관이 있더라. 아,
+&gt;&gt; 영화 보는 방이 있긴 해요.
+&gt;&gt; 동굴 같은 곳입니까?
+&gt;&gt; 동굴은 동굴은
+&gt;&gt; 아, 동굴도 뭐 협수한 동굴들이
+있으니까.
+&gt;&gt; 예. 여기도 동굴이라고는 안 했고
+동굴 같은 곳이다.
+&gt;&gt; 음. 사람에 따라 그렇게 볼 수도
+있을 것
+&gt;&gt; 같죠. 오케.
+&gt;&gt; 자, 이것도 맞습니다. 오케이. 자,
+두 번째 맞습니다. 자, 세 번째
+&gt;&gt; 집에 사우나 스크린 골프장 당구장
+수영장 있다.
+&gt;&gt; 아, 수영장은 없고
+&gt;&gt; 아, 수영장은 아니고 당구장.
+&gt;&gt; 당구대는 있습니다.
+&gt;&gt; 당구장. 자, 당구장은 아니고 당구
+대는 있다. 자, 스크린 골프장.
+&gt;&gt; 어, 네. 있어요. 자, 그러면 집에
+사우나 스크린 골프장 당구되는이
+좋습니다. 수영장은 없습니다.
+&gt;&gt; 아, 집안에 집안에 스크린 골프를 칠
+수 있어요?
+&gt;&gt; 있더라고요.
+&gt;&gt; 아, 그 공간을 아,
+&gt;&gt; 네. 그 가끔 씁니까?
+&gt;&gt; 저 거의 집을 많이 못가 가지고.
+&gt;&gt; 어, 그럼 그거 누가 써요?
+&gt;&gt; 보통 이제 친구들이랑 좀 모임 같은
+거 할 때 같이 네.
+아니 진짜 영앤 리치 사드 찾을 거
+없어. 페이커가 영앤 리치야.
+&gt;&gt; 아 참 대단하네 진짜 정말.
+&gt;&gt; 네.
+&gt;&gt; 아유
+&gt;&gt; 장합니다. 장해 장해. 근데 그
+&gt;&gt; 그럴 만해. 이게
+&gt;&gt; 이게 지금 하는 그이 게임 시장이
+이거 산업이에요. 어마어마해.
+&gt;&gt; 근데 그만큼 페이커시가 나가서 놀고
+싶었다고도 계속 연습을 했겠어.
+&gt;&gt; 나는 근데 그게 궁금해요. 그 어렸을
+때 부모님께서 게임을 워낙 좋아했을
+거 아니에요.
+&gt;&gt; 네. 밤 세고 게임했죠?
+&gt;&gt; 밤은 안 셌어요.
+&gt;&gt; 안 셌어요?
+&gt;&gt; 그럼 딱 그 시간 지켜 가지고
+&gt;&gt; 저도 학교 가야 되니까 거의 자정은
+안 넘겼던 거 같아요.
+&gt;&gt; 아 진짜?
+&gt;&gt; 네. 자정은 거의 안 넘.
+&gt;&gt; 그럴 때 좀 집에서 들었던 얘기
+있습니까?
+&gt;&gt; 뭐 적당히 하고 자라 그런 얘기
+하시는데 또 저는 적당히 하고 자긴
+하니까
+&gt;&gt; 네. 별말 안 하셨던 거 같아요.
+&gt;&gt; 아 그리고 진짜 게임을 하는데도
+상당히 또 이게 뭐라 그럴까? 즐킬
+거 딱 키니까 돌을 넘지 않네.
+&gt;&gt; 그렇죠. 아, 그래서 또 요즘 많은
+분들이 페이커한테 열광하는데 그런
+거야. 물론 잘하니까 그런 것도
+있지만 뭔가 탁 지켜야 될 그니까
+한마디로 좀 풍격이 있어. 이거
+굉장히 중요하거든요. 페이커가 풍격이
+있어.
+&gt;&gt; 네, 맞아요. 평소에 님 뭐 뭐 할
+때 제일 좀 행복하고 쉽나요? 게임을
+제외하.
+&gt;&gt; 음. 저는
+책 볼 때가 제일 그 최근에는
+&gt;&gt; 책 볼 때가 제
+&gt;&gt; 책 최근 배거 최근 말
+&gt;&gt; 편한 거 같아요. 네.
+&gt;&gt; 최근에 뭐 본 책이 뭡니까 혹시?
+최근에는 저는 이기적 유전자 보고
+있는데
+&gt;&gt; 야 책을 보는
+&gt;&gt; 네
+&gt;&gt; 아니 근데 페이커가 전 갑자기 그런
+생각이 들었어요. 이렇게 전체적인
+느낌이 만약에 게임을 안 했다
+하더라도 바둑 쪽으로 갔어도 아
+&gt;&gt; 아마 아마 했을 거야 집중력이나 여러
+가지가 아 굉장히 뛰어난 거 같아요.
+&gt;&gt; 뭔가 본인만의 어떤 루틴이 있을 것
+같아요. 딱
+&gt;&gt; 음
+&gt;&gt; 게임하기 전에
+&gt;&gt; 게임하기 전에
+&gt;&gt; 이제 뭐 자리를 이렇게 한다거나
+방석을 어떤 거 좀 깐다거나 뭐
+&gt;&gt; 근데 게임할 때 아무래도 자세가 조금
+달라지면은 그 쓰는 근육이
+달라지거든요. 예를 들면은 팔이
+이렇게 돼 있을 때랑 이렇게 돼 있을
+때랑 다르거든요. 쓰는 근육이.
+그래서 자세는 되게 일정하게 하려고
+하고 있긴 해요.
+&gt;&gt; 아,
+&gt;&gt; 야, 이게 사실은 뭐 하루 종일 아,
+이게 쉬없이 이게 이제 움직여야
+되니까.
+&gt;&gt; 네. 맞아요.
+&gt;&gt; 대회전에 손목 부상으로 한 달간 좀
+리그를 추천을 못 하셨다 그래요.
+&gt;&gt; 네, 맞아.
+&gt;&gt; 예.
+&gt;&gt; 한 3개월 전에 갑자기 새끼 손가락이
+엄청 절이고
+&gt;&gt; 아,
+&gt;&gt; 되게 감각이 없는 거예요. 게임하고
+나면. 음. 그래서 좀 해보자 했는데
+계속해서 좀 증상이 안 좋아 가지고
+좀 한 달 정도 쉬고
+&gt;&gt; 뭐 형 괜찮아 막 이렇게 오긴 하는데
+안 괜찮아 가지고 이렇게 먹으라고 해
+주기가
+애매해서 그냥 별로 괜찮지 않았는데
+그냥 뭐 이응 이응 이렇게 보내고
+그랬던 거 같습니다. 그게 딱 상상경
+빠지면서 딱 다 뭔가 이렇게
+연세적으로 다 터지면서 컨디션도 안
+좋고 상태도 안 좋아지고 경기력도
+되게 안 좋아지고 서로 봐 실뢰도 안
+좋아지고
+그냥 뭔가 대회장 갈 때
+약간 맞으러 가는 느낌 이런 기분이
+좀 들었거든요.가
+아픈데도 그냥 경기장 좀 같이
+따라와서 같이 응원해 주고 약간 그런
+모습들이 눈에 보였었는데
+저희 팀의 문제점이나
+좀 개선들이 제 부상으로 인해서 좀
+많이 보인 거 같아서 그런 것들은
+오히려 긍정적으로 많이 된 거
+같아요.
+&gt;&gt; 복귀를 하고 나서 어떤 역할을
+해야겠다 그런 것들을
+많이 고민했던 거 같아요.
+&gt;&gt; 제가 좀
+&gt;&gt; 아프기 전까지 몰랐는데.
+&gt;&gt; 네. 아프고 나니까 확실히 좀 관리를
+해 줘야겠다라는 생각이 좀 들긴
+하더라고요.
+&gt;&gt; 다른 뭐 좀 관리하는 거 있습니까?
+&gt;&gt; 뭐 스트레칭이나 좀 가벼운 운동 같은
+거 좀 하려고 하고 있습니다.
+&gt;&gt; 스트레칭 뭐 해요? 우리 페이커
+&gt;&gt; 저는 뭐 이런 거나
+&gt;&gt; 네네
+&gt;&gt; 이런 거나
+&gt;&gt; 그리고
+&gt;&gt; 손목을 많이 쓰니까
+&gt;&gt; 그리고요
+&gt;&gt; 이게 근데 손목네 팔쪽 스트레칭도
+돼서
+&gt;&gt; 아 맞아요 맞아요
+&gt;&gt; 스트레칭은 저기 잠깐만 페이커 이거
+끝이에요
+&gt;&gt; 아 이게 이게 여기 8쪽 스트레칭이랑
+이게 제일 중요해서 그 예 그리고
+&gt;&gt; 스트 뭐 요거 비슷한 거 좀 하고
+&gt;&gt; 아 요거이 좀 돌려주고
+&gt;&gt; 어깨 좀 돌려주고
+&gt;&gt; 사실 스트레칭이 저는 진짜 별게
+없다고 생각해요.
+근데 이게 되게 중요하다고
+&gt;&gt; 정말 딱 게임에 필요한 스트레칭.
+&gt;&gt; 네.
+&gt;&gt; 손목
+&gt;&gt; 하고
+어깨
+&gt;&gt; 그리고 바로입니까?
+&gt;&gt; 아 근데 꾸준히 하는게 중요합니다.
+네.
+&gt;&gt; 혹시 그러면 약도 드시나요? 뭐
+관절약이나 루테인 같은 거제 눈에
+좋은 거.
+&gt;&gt; 저는
+&gt;&gt; 왜냐면 이제 화면을 많이 보니까음
+&gt;&gt; 저는 비타민 먹어요. 비타민. 비타민
+먹는데
+&gt;&gt; 페이커 선수가 진짜 말 그대로
+핫합니다. 예. 이게 SNS 뭐
+인터넷 그래서 이제 페이커 도서리스트
+페이커 플레이스트
+페이커 얼어 온통 페이커로 지금 뭐
+도배가 된 상태예요.
+&gt;&gt; 아 진짜요? 어 그럼요. 예.
+아, 우리 전설의 프로 게이머
+페이커의 어록입니다.
+&gt;&gt; 어,
+&gt;&gt; 우승을 밥 먹듯이 하다 보니까 또
+우승을 해 버렸네라는 생각이 드네요.
+&gt;&gt; 인간관계에서 상처받지 않으려면 남이
+버린 쓰레기를 내 주머니에 넣으면 안
+돼요. 내 주머니만 더러워지잖아요.
+아,
+&gt;&gt; 여러분 기부도 좋지만 맛있는 거
+사드세요. 기부는 저처럼 돈 많은
+사람들이 하면 됩니다.
+&gt;&gt; 아, 야, 이건 키가 막히다.
+&gt;&gt; 이거 본인이 한 얘기 다 맞죠?
+&gt;&gt; 아, 맞는 거 같아요.
+&gt;&gt; 어, 그래요? 아, 근데 사실 뭐
+기부 관련해서는 이게 좀 공석에서
+한게 아니라서
+&gt;&gt; 그냥 사석에서 한 건데.
+&gt;&gt; 네. 약간 재미로 한 거긴 한데.
+&gt;&gt; 아, 그렇지. 아, 이제 사석에서
+&gt;&gt; 아, 이게 네. 사석은 아닌데 개인
+방송에서 팬분들이 너무 저한테 후원을
+많이 해 주셔 가지고 뭔지 알겠다.
+&gt;&gt; 대신에 좀 네. 그렇게 하지 마시라고
+약간 좀 농담 상황적으로 얘기
+들으니까 뭔지 알겠네. 네, 맞아요.
+그니까
+&gt;&gt; 그 최근 요게 화제입니다. 페이커
+선수가 이제 팬미팅에서 YB에 너를
+보내고
+[음악]
+&gt;&gt; 네. 요거를 이제 노래를
+하셨다고 했는데 그 요래를 평소에 좀
+좋아하세요,이 노래를.
+&gt;&gt; 제가 그때
+&gt;&gt; 작년에 팬 미팅이 있는데
+&gt;&gt; 팬분들이 갑자기 노래해 달라고
+해가지고 하여. 근데 팬분들이 하면은
+또 거절할 수가 없으니까.
+&gt;&gt; 근데 이게 또 페이커가 참 우리 팬
+여러분들을 위한 마음이 참 또
+애뜻하네. 특별하고.
+&gt;&gt; 네. 그렇죠.
+&gt;&gt; 근데 연말이어 가지고 아, 또 뭔가
+특별한 경험 또 드려야겠다.
+&gt;&gt; 막상 이게 또 준비가 안 돼 있으면은
+사실은 갑자기 노래 이제 마음이야.
+그렇지만
+&gt;&gt; 제 진짜 준비가 하나도 안 돼 있어.
+&gt;&gt; 아, 그러니까
+&gt;&gt; 왜냐면 대본에 없었거든요.
+&gt;&gt; 대본에 없었는데 갑자기 제 노래는
+별로 좋아하지 않았어요.
+&gt;&gt; 오늘도 좋아.이 이 기쁜 마음을
+노래로 혹시
+&gt;&gt; 와이비에 너를 보내고 한번 좀
+부탁드려 돼요? 너 보살
+&gt;&gt; 언저리마다
+너를 남기고 돌아서는
+&gt;&gt; 우와
+&gt;&gt; 내게 시간은 그만 놓아주라는데
+우와
+&gt;&gt; 여기까지
+&gt;&gt; 근데 괜찮다
+&gt;&gt; 좋은데 좋은데
+&gt;&gt; 아 와이비의 느낌이 있네 느낌이네
+느낌이네
+&gt;&gt; 아 있어요
+&gt;&gt; 와이비의 느낌이 있어
+&gt;&gt; 아닙니다 진짜 이거 빈말이 아니라
+느낌이 있어
+&gt;&gt; 아 나도 약간 그랬어
+&gt;&gt; 이게 노래를 좋아하는 거랑 좀 잘하는
+거랑은 자꾸 게 잔데. 아, 그래도
+노래
+&gt;&gt; 아니 그 느낌이 있다니까. Y이
+느낌이 좀 있어. Y비를 좀 좋아하나
+봐요. 그죠?
+&gt;&gt; 아, 네. 좋아합니다.
+&gt;&gt; 그 플레이리스트는 혹시 뭐 요즘 즐겨
+듣는 노래 있습니까?
+&gt;&gt; 저는 요즘 가사 없는 거 많이 듣고
+있어요.
+&gt;&gt; 경호막 뜯으세요?
+&gt;&gt; 클래식? 클래식?
+&gt;&gt; 네, 클래식.
+&gt;&gt; 아,
+&gt;&gt; 또 듣는데 요즘에는 오히려 뉴에이지
+많이 듣는 거.
+&gt;&gt; 아, 뉴에이지? 아, 요즘 또 이제
+우리 그 페이커가 뉴에이지를 좀 많이
+듣는 거죠.
+&gt;&gt; 아까 제가 목표에 대해서 말을 했는데
+&gt;&gt; 또 재석님의 궁극적인 목표가 무엇인지
+&gt;&gt; 아, 저의 목표요?
+&gt;&gt; 인생에서. 아, 그니까 제가 이제
+저 목표가 없어요.
+&gt;&gt; 아, 목표가 없어요.
+&gt;&gt; 목표가 없어요. 그냥 뭐 늘 다른
+분들도 똑같이 생각하는 거지만 그냥
+건강하게 그냥 행복하게 그러니까
+그거는 좀 비슷한 거 같아. 페이커랑
+&gt;&gt; 나뿐만 아니라 뭐 이게 가능하다면
+많은 사람들과 함께 행복했으면
+좋겠어요.
+&gt;&gt; 나만 행복하면 재미가 없으니까.
+&gt;&gt; 그리고 나 혼자 행복한 거 행복이
+아니잖아요. 그 나 혼자 행복하면
+뭐해? 시간이 지나서 나이를 더
+먹더라도 마음껏 좀 주변에 베풀 수
+있는 사람이면 좋겠어요.
+&gt;&gt; 그니까 베푼다는 표현이 그렇지만
+마음껏 내가 밥 먹었을 때 그런 거
+그냥 충분히 그냥 아무렇지 않게 그냥
+계산할 수 있고
+&gt;&gt; 이러면 좋겠어요.
+&gt;&gt; 예. 현이 되게 되게 현실적인 거
+같아. 그렇기 때문에
+&gt;&gt; 그러니까 내가 간단해 쪼들리기
+싫어요.
+&gt;&gt; 예. 나이 들어서 쪼들리기보다는 좀
+페이커는 어때요? 궁극적인 목표가 있
+&gt;&gt; 아 저는 근데 좀 공감이 됐어요.
+약간 그런 마음이 남아 있다. 있어야
+된다는 의미로 저는 좀 들려가지고 예
+&gt;&gt; 그럼 베풀 수 있는 마음이 남아
+있어야 된다라고 들어 가지고 그게
+너무
+&gt;&gt; 맞아요.
+&gt;&gt; 와닿던 거 같아.
+&gt;&gt; 예. 뭔가 그러려면은 내가 어 사실
+돈도 많이 벌어놔야 되고 일도 열심히
+해야 되고 지금 또 할 수 있을 때
+어찌 됐든 뭔가 나이 들어서도 이런
+거 저런 거 다 제끼고 그냥 폼이 안
+떨어지고 싶어요.
+&gt;&gt; 아 그럼요.
+&gt;&gt; 예.
+이 폼 그냥 유지하면서 살고
+싶습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>언젠간 보게 될 마지막.. 준비되셨나요?💔</t>
+          <t>“결국 페이커 바짓가랑이 붙잡고 기대했잖아“ -도파</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=trbqgkf-9fI</t>
+          <t>https://www.youtube.com/watch?v=3Qv88zFeQZM</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>롤린LOL린</t>
+          <t>SHORT TUBE</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UChsa-B7FJao_YXtQ1d-dXXg</t>
+          <t>https://www.youtube.com/channel/UCpMU2iFYOsk5zMkef6ajJDw</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>375665</t>
+          <t>234,754</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>19300</t>
+          <t>3,410</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2025-08-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>2024-11-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>SKT n 그냥 다 필요
+없고 그 그냥 그 페이커의 그 경력
+때문에 항상 볼 때마다 약간 믿음이
+가잖아요 결국 그 마지막에 붙잡을 거
+없을 때 바지가 다 페이커 바지가랑이
+붙잡으면서 기대하잖아 솔직히 다 까는
+애들도 마지막에는 결국 그 한 팀밖에
+안 남으면</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>동생들에게 고맙다고 소감 말하는 페이커ㅠㅠ</t>
+          <t>유일하게 커즈를 투표했던 페이커</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=U7-MxGyFhBQ</t>
+          <t>https://www.youtube.com/watch?v=hMZ8_rc_QwU</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>숭배하라</t>
+          <t>롤한입</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UChT_3672e3gi9TzLUCpvDow</t>
+          <t>https://www.youtube.com/channel/UC6ZeliIDAOqjz5u-_1g0iRg</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>153515</t>
+          <t>267,690</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>35600</t>
+          <t>3,240</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2025-08-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>2025-09-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>세컨 정글 투표에서 수많은 사람들 중
+유일하게 커즐을 찍은 단 한 사람
+페이커요.
+와
+야라고
+생각도 했는데 그게 아니었어요. Eh</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>구마유시의 잡기술에 당해버린 페이커 ㅋㅋㅋㅋ</t>
+          <t>[KLEVV x T1] 만들어 봐, 네 본체의 빛</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=FlHV-MBNotY</t>
+          <t>https://www.youtube.com/watch?v=KUeq__RmAjE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>롤 Empire</t>
+          <t>KLEVV</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCTYlu-5_kM1HqV2nKl0V9hQ</t>
+          <t>https://www.youtube.com/channel/UCOVODzUrXFJcjx6Wfs4Eu6g</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1233280</t>
+          <t>8,436,175</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3660</t>
+          <t>6,940</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2025-09-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>2020-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>아
+[음악]
+부정 거 줄래 내 램 좀 보게
+hana lee
+오늘 내 리본 걸로 로 바랄께요 we are the bs lee sm
+암이
+더워질 것
+tv 타로와 및 선체 내 미 되고 싶어
+we 알고 싶어 널 rgb 껏
+own the
+만들어봐 2 본체 ep the be the
+[음악]</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>소름주의ㄷㄷ 페이커 재계약 공개 현장반응ㄷㄷㄷ</t>
+          <t>총을 대충 쏘면? (ft. 페이커)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NKlih-EEv-8</t>
+          <t>https://www.youtube.com/watch?v=UdLyoe-SvvE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>레고를밟았네-롤차트</t>
+          <t>T1 Esports</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCwhXBKRvKlAQMHPZnpSevYw</t>
+          <t>https://www.youtube.com/channel/UCFKoZGmbCbIN5nKi-zlIcmw</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>7977390</t>
+          <t>2,034,839</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>6820</t>
+          <t>317,000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2025-07-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>2022-09-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>총알 대충 쏘는 걸 뭐라고 할까요
+감사합니다
+[음악]
+[음악]
+팔러서
+[음악]
+오늘 왜 이렇게 웃음이 나오지 아니
+그 뭐지 뭔가 오늘
+웃음이 많이 나오네
+[음악]
+[음악]</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>자꾸 돌고있는 오구케의 손목 이슈 #t1 #lck  #페이커 #도란 #오너 #구마유시 #케리아 #shorts</t>
+          <t>페이커 스트리밍 중 난입한 4인방..?!?</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=OeJPJMcVBAI</t>
+          <t>https://www.youtube.com/watch?v=WUl52HFioAE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>대유쾌마운틴</t>
+          <t>T1 Esports</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCBjjh72yM1KoMHfFhNBQr8w</t>
+          <t>https://www.youtube.com/channel/UCFKoZGmbCbIN5nKi-zlIcmw</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>357656</t>
+          <t>3,620,401</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>44300</t>
+          <t>317,000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2025-09-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>2022-05-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>5
+[음악]
+으
+5
+아아아
+뭐 주인공 하세요 예
+에
+photo
+보세요
+여야와 이루어져 걸어 아 이게 오면
+안 된 솔직히 안된 솔직히 네 손
+생보 봐
+철망
+[음악]
+으
+아
+1622 좀 바빠서 써 없는 내가 좀
+안 좋은 타이밍에 들어 이 거리라도
+빨게 생각해요
+안녕하세요
+제대로 봤다 아</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>" 페이커는 망설이지 않는다 "</t>
+          <t>페이커의 방에 찾아온 척추요정</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=JFmK88LO7uY</t>
+          <t>https://www.youtube.com/watch?v=FZ_77UBmAxQ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DaeHyun</t>
+          <t>롤창고</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCFvQpH3ZAkW7_Y4WkvrFYbQ</t>
+          <t>https://www.youtube.com/channel/UC_tVTCJud5Gq6Od9Dqfj48A</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1544776</t>
+          <t>6,265,479</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>44700</t>
+          <t>4,900</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2025-08-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>2025-03-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>페이커의 방에 찾아온
+척추요정 안녕난 척추
+요정이야 저 오늘부터 진짜 바른
+자세합니다 왼쪽 아래 저 하
+뭔가요 저의 무릎입니다
+어떻게 저렇게 쭈그리고 앉아서 게임을
+잘할까 수술만 원 척추 수술
+2500만 원
+감사합니다
+중요하죠 들
+안녕
+합니다 어 이거 보니까 척추 펴야겠다
+확실히
+어 척추 건강 중요하죠
+[음악]</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>갑자기 서렌치는 페이커ㅋㅋㅋㅋ</t>
+          <t>페이커가 누구야? (10주년 헌정)≪페이커(FAKER)≫4번째 우승 풀스토리🔥 G.O.A.T🐐  아마추어 고전파부터 전설의 월즈 4회 우승 GODS유퀴즈</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BnccRToU2BA</t>
+          <t>https://www.youtube.com/watch?v=m4lqJUK_rMU</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>롤숭배</t>
+          <t>아리tv-롤정보통</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UC-xgOG-CsVXlt7dth87uHbg</t>
+          <t>https://www.youtube.com/channel/UCzGblRaF5unKKz10hACKGDg</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2615037</t>
+          <t>512,201</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>63,700</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2025-08-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>2023-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>정말 멋진 경기 패쳐 준 SK 장
+그죠 승이 승이의 이런 어가 있으면
+아 페이커의 저는 아 안주면 뿐이겠죠
+할 수 있다 우리한테 판은 깔렸다
+모두 팀으로 외쳤다 왔다 왔다 아
+잘해 오자
+렉스가이 말도 안 되는 스토리를
+완성시킵니다 아 까이다 얘들아 얘들아
+다거 고했다 같이 같은 꿈을 꿨던
+선수들도 많거든요 바로를 떨고 있는
+캐리아 정말 잘했습니다
+네 번째 우승을 노리고 있는 고트
+페이커 절대로 우승을 놓치지 않을
+것네 번째 우승은네 번째 우승은
+네번째
+[음악]
+우은 저는네 게임 게임을 어렸을
+때부터 좋아하긴 했는데 그전 빼고는
+그냥 평범한 학생이던 거 같아
+페이커는 1996년 5월 7일생으로
+어린 시절부터 책읽기를 좋아하는 범한
+소년이었습니다 할머니와 아버지 그리고
+남동생과 함께 자라온 페이커는 기초
+생활 수급 지원을 받을 정도로 어려운
+형편이었습니다 하지만 학창 시절 꿈이
+대통령이었습니다 정도로 공부도 잘하고
+성격도 착한 학생이었습니다 어느 날
+우연히 아버지의 지원으로 컴퓨터
+게임을 접하게 되면서 그의 인생은
+완전히 180도 바뀌게 됩니다 어렸을
+때부터 집에 컴퓨터가 좀 일찍
+들어와가지고 어렸을 때부터 게임도
+많이 하고 메이플 스토리부터
+스타크래프트 그리고 카오스 친구들과
+함께하는 게임을 즐겨 있었던 페이는
+중학교 때 자신이 다른 사람들보다
+재능이 뛰어나다는 것을 알게 되는데
+사실
+롤에 제가 또 재능이 어느 정도
+있었기
+때문에은 제가 중학교 3학년 때 시
+됐었거든요
+그때부터 그렇게 한창 게임에 빠져
+있을 때 한국의 리그 오브 레전드가
+들어오게 되면서 다른 여느 사람들처럼
+롤래 빠지게 되었고 전설은 시니다네
+그래서 친구들이랑도 많이 하고
+온라인게임 다하게 했가 센스가
+그때부터 좀 늘지 않았나 생각합니다
+이전부터 남달랐던 게임 센스와 특유의
+집중력으로 게임을 즐기는 것뿐만
+아니라 많은 연구를 통해 게임 실력을
+높여 갔습니다 무서워 가지고
+랭크게임을 많이 못 했는데 그래서
+노마를 많이 하다가 일반 게임을
+500판 넘게 하며 너무 레이팅이
+높아지자 랭크 게임에 눈을 돌린
+페이커 자 배치고사를 봤는데 그때부터
+좀 점수가 계속 쭉쭉 올라갔던 거
+같습니다 특별한 케이스인게 약간
+처음부터 계속 점수가 올라서
+챌린저에서 밖에 유지를 한 적이
+없어서 전설 로 불리는 고전은 천상계
+유저들 사이에서도 소문이 자자할
+정도로 아마추어 은둔
+고수였던는 다이아몬드에서 정체된 적이
+없었기 때문에 잘 모르겠고요 압도적인
+점수로 한국 랭킹 1위를 찍어
+버립니다 전파가 즐겨 사용하던
+챔피언은 바로 신드라 있는데 그 당시
+주류 챔피언은 아니었지만 뛰어난
+피지컬로 신드라 장인으로 불리고
+있었죠 천상계 솔랭 전파 때문에
+신드라를 변하기도 했습니다 이때
+페이커의 나이는 17 살이었고 그의
+실력을 알아본 많은 프로 팀들이
+제일을 보내기 시작합니다 취미로
+하다가 딱 제희가 오니까 그때
+결심했던 거 같아요 당시 페이커는
+진지하게 고민을 할 수밖에 없었습니다
+게임에 재능이 보이면서 뭔가 공부하는
+거보다는 게임하는 걸 많이
+좋아했거든요 프로게이머라는 직업이
+지금처럼 많지도 않았고 공부도 상위
+10% 안에 들 정도로 잘했으니
+말이죠 시절 때 공부를 상위권 정도는
+유지하는 학생이었는데 하지만 만약
+실패를 하더라도 인생에 큰 교훈이 될
+거라는 리듬을 가지게 된 페이커는
+당시 자신에게 손을 내밀어 준 김정균
+감독의 제안을 수락하고 SKT
+입단하게 됩니다 그때 당시에 프로게임
+단들이 마침 생기기 시작할 때라서
+저를 스카우트 하셔 가지고네 그때부터
+좀 프로게이머 생활을 시작했던 거
+같습니다 그렇게 아마추어 최고수 고전
+판는 역사 속으로 사라지고 리그 오브
+레전드 역사상 최고의 선수이자 롤 그
+자체인 페이커가 탄생하게 되었죠
+안녕하세요 저는 SK 텔레콤 T1
+이드라인
+페이커의 의미는 속이는 사람이라는
+뜻으로 자신의 플레이스타일과 맞고
+멋있어 보여 고르게 되었다고 합니다
+아 이텔 T1이 팀은 솔로랭크에서
+엄청난 경기력을 보여줬었던 선수들
+위주로 이제 구성이 되었고 그렇게
+sktt1 2팀으로 들어간 페이커는
+2013년 4월 6일 당시 강팀으로
+명성을 떨치고 있었던 CJ 엔투스와
+만나게 되는데요 그런 면에서 오늘
+첫경기에 얼마나 대단한 경기를
+보여줄지 기대요
+첫 처 올라가기도 했었고 그냥 경기를
+하겠구나 하는 그렇게 막 긴장되거나
+떨리거나 그 않 데뷔전의 상대는 당시
+세계 최고의 미드라이너로 불리는 비의
+강남이라는 것은 말할 필요가 없죠
+급입니다 그렇습니다 뭐 정말 내로라는
+세계 정말 몇대 미드 안해도 충분히
+만한 그런 선수라는 평가를 받고
+있고요 과연 첫 대비한 아마추어
+장인이 프로무대도 까라 많은 이들의
+주을 받게
+되었죠 선수와 오늘 엠비션의 싸움이
+굉장히 흥미진진합니다 싸움이 된다라는
+지금 평가가 지배적이기 때문에 과연
+엠비션 선수를 상대로 어떤 모습을
+보여 게요 엠비션은 첫 대비한 상대라
+방심에서 있지 페이커의 눈앞에서
+진화를 하게 되고 골드에
+영향을습니다 그 장면을 놓치지 않은
+페이커는 과감하게 파고들어 무려
+솔기를 만들어냅니다 아 역시 고등학생
+무섭네요네 지금 약간 션 선수가 그냥
+6 타이밍에 진화하다 죽은 거
+같았거든요 지금 만 아니라 전체적인
+경기력까지 한수위의 모습을 보여주며
+CJ 엔투스를 2대
+0으로부터 모두 MVP 선정되며
+엄청난 화제가 되었죠 번째 경기
+MVP 페니다 와 두 경기 연달한
+MVP 화려한 등장과 함께 첫 대뷔
+시즌을 3위로 마친 SKT 페이커는
+다음 서머에서 더 발전된 모습을
+보여주며 승리해 나갔고 16강에선
+카사디 제드 오리아나 그라가스 아리
+신드라가 각기 다른 챔피언으로 6전
+전승으로 미드를 압살했다 스킨 흡수
+당했어요 스킨수
+당했습니다
+어 했는데요 아 이번에 빠져 전멸이
+없잖아요 자 이거 한번
+스킬 18 경기에서 18 솔기를 따낼
+정도로 괴물 같은 피지컬을 보여줬고
+결국 파이널에 진출하게 됩니다
+챔스
+결승
+팀
+만나보겠습니다 상대는 압도적인 기세를
+자랑하던 티였다 페이커가 있는 SKT
+쉽지 않은 상대였어 그렇게 시작된
+대망의 세트에선 케이티의 타워를
+하나도 제거하지 못하고 무기력하게
+패배하는데 좋긴 좋았지만 타고하는
+전투 최 두번째 경기도 이렇다할
+반격을 해보지 못하고 패배하며 페이커
+신드롬은 여기서 마무리 되나
+싶었습니다 하지만 세 번째 세트에서
+당시 압도적인 피지컬로 화려한
+플레이를 자랑하던 제드 꺼낸 페이커는
+류의 그라가스를 압도하며 역전의
+발판을 마련했죠
+했습니다
+아 말릴가 없어 기세를 몰아
+4세트까지 승리한 SKT 당시엔
+블라인드 픽으로 진행되던 마지막
+5세트로 향하게
+되는데는 무조건 세트입니다 여러분
+넥지면서 그 이후로 10년 동안 계속
+죽게 될 페이커와의 제드 미러전
+명장면이 탄생합니다
+그렇게 패승승으로 대비한지 두
+시즌만에 우승을 차지한 페이커는
+대망의 월드컵으로 향하게
+되었습니다 다시 이번 시즌의 왕자에
+올라 결승에서 사의 여한 라이벌
+게이트
+정말 많은 것을 얻어가네요 LCK
+승격으로 리그오브레전드 최 불리는
+월드 챔피언십에 참여하게 된 페이커
+그 당시만해도 지금과 다르게 LCK
+성적은 참혹한 편이었죠 국내 대회에선
+막강한 실력을 자랑하던 SKT 있지만
+세계 무대는 호락호락하지 않았기에
+팬들도 반심 반이 하던 상황이었습니다
+하지만 페이커에 엄청난 피지컬을
+앞세운 SKT 팬들의 우려를 싣고
+막강한 모습을 보여줬는데요 인상깊은
+경기라 하면은 처음에 제가 우승했던
+그 경기가 가장 기억에 남는 거
+같아요 상대는 중국의 강팀 로얄
+클럽이지만 결승전이라는 것이 허무할
+정도로 압도적인 3대 0이라는
+스코어로
+우승했고 전세계에 페이커라는 이름을
+알리게
+되었죠 지금과 다르게 그 당시엔 윈터
+시즌이 있었는데 여기서도 페이커는
+막강했습니다 결승전에 진출한 페이커는
+당시 상대팀의 미드였던 다대를 3분
+만에 솔킬을
+했고 임프마법사
+페이커는 막을 수 없었고 세 경기
+모두 MVP 받으며 페이커의 시대를
+선언했습니다 하지만 그 기세도 잠시
+스프링과 서머에 팀 자체가 이렇다할
+성적을 내지 못했고 겨우 진출한
+롤드컵 선발전에서도 아쉬운 모습을
+보이며 여느 다른 선수처럼 반짝이는
+건가 싶었습니다 더군다나 sktt
+1이 다닐 팀으로 탄생한 첫시즌
+결승전에선 페이커 대신 이지훈이
+출전하며 떨어진 폼이 돌아오지 않았죠
+많이 응원하면서 봤는데 제가 나갈
+필요도 없이 너무 잘해가지고
+아 아쉽네요 MSI 때는로 나도록
+하겠습니다 하지만 페이커는 절대
+포기하지 않았습니다 수많은 노력으로
+누구보다 자신 있었던 폭넓은 챔피언
+폭을 적극 이용하기
+시작했죠
+그리고 드디어 결승에 진출한 페이커는
+마지막 3세트에서 누구도 하지 않던
+리을 픽하여 캐리를
+보여줬고
+다시 한번 우승을 들어올립니다
+그렇게 돌아온 페이커는 또 한번 월드
+챔피언십 결승에 진출했고 슈퍼스타다
+모습을
+보여주는데
+타이거즈와 마지막 경기에서 자신의
+상징과도 같은 라이즈로 무려 킬관여율
+100% 기록하며 월즈 2회
+우승이라는 대기록을 세우게
+됩니다
+2016년도 완전 페이커에 해였습니다
+다음 시즌인 2016년엔 멤버들이
+조금 바뀌긴 했지만 페이커는 흔들리지
+않습니다 스프링 우승과 MSI
+우승까지지며 월드 챔피언십으로 향하게
+되었죠 들
+빙을 는 대망의 결승 마지막
+5세트에서 롤드컵 최장기간 경기 끝에
+룰러의 삼성을 상대로
+승리했고 통합까지 검어지며 롤드컵
+3회 우승이라는 엄청난 대기록과
+아마추어 신드라장인 고전에서 역이
+페이커라는
+타이틀에었습니다 하지만 그렇게
+승승장구하던 페이커도 프로무대에서
+계속 정상을 차지하는 건 쉽지
+[박수]
+않습니다 넘치는 신인들의 장과 더불어
+최고의 자리에 있을 때 따라오는 부담
+그 약간 쏟
+년에는과 달 복이
+한이지만 기는 슈퍼플레이
+[박수]
+전했 강에서 중국의 강팀를 상대로
+5연속 갈리오를 꺼내며 팀을 결승으로
+이끌었죠 하지만 다시 만난 삼성과의
+결승전은 페이커 마저 무너지며
+무기력하게 3대으로
+패배했고
+그 구보다를 간절했던 페이는 을지도
+못한채 거운
+[박수]
+눈물을습니다 을까 완전무결한 모습을
+보여주던 페이커는 전엔 하지 않던
+실수가 많아졌고 항상 보여주던 상대를
+압도하던 모습은 점점
+사라져갔습니다 처음보는 페이커의
+부진의 호시탐탐 기회를 노리던
+안티들은 이때다싶어 그를 공격했고
+비난의 수위도 점점 올라갔죠 성숙한
+성인들 조금의 욕이나 비난을 들어도
+멘탈을 잡기 쉽지 않은데 만개의
+악플을 견디는 페이커의 기분은
+어땠을지 어 이거 안 좋아 안 좋아
+야 이거 아 끝났다 아 끝났다 길을
+찾는데 갈수록 해고 다음에 더 잘할
+수 있을지 확신히 없어 누구라도
+포기하고 싶을 상황이었지만 페이커는
+포기하지 않았습니다 좀 더 방향을
+찾아야 될 것 같아요 더 노력을 해야
+될 것 같고요 평소 취미였던 독서와
+명상 그리고 스포츠 심리상담지 받으며
+부진과 불안을 극복하려 노력했습니다
+더 우승을 할 수 있는 방향으로 힘이
+있었으면 좋겠다는 생각이고요 만약
+그런 것들을 없다면 좀 되게 힘든
+삶일 것 같아요 어려운 삶일 것
+같아요 그렇게 페이커는 조금씩 기량을
+끌어올림과 동시에 좋은 동료들을 만나
+LCK 우승컵을 들며 화려한 부화를
+알리는 듯했죠 그리고
+뒤를
+결 호 SKT 적 l 일곱 번째 우승
+넥서스를 깨면서 SK
+텔레콤 여덟 번째 우승을 차지한 SK
+텔레콤
+원 하지만 국제 대회에선 예전에
+위험과는 다르게 고전을 면치 못했고
+성적도 따라오지
+않았습니다 바론이 어떤 발언이 아
+페이까지 한번
+에투가 SK 텔레콤을 막지 가는 점
+끝에 넥 를 깨면서 이것은 최제
+심지어 상대 mlxg 이런 말을
+남기기도
+했습니다 이때부터였을까요 역시 프로
+게이머의 수명은 짧고 그 대단한
+페이커조차 나이를 이기진 못한다
+이제는 은퇴를 준비해야 하는게
+아닐까라는 반응도 나오기 시작했습니다
+하지만 그럴 때마다 페이커는 스스로
+자신을 증명했습니다 과거에 누구를
+만나던 상대를 찍어 누르는 압도적인
+무력의 페이커 있다면 이제는 노련한
+경험과 관로 으로 자신이 아닌 팀이
+승리하게 만드는 운영을 보여주기
+시작했죠 리언 리언 터졌어요 나가 또
+앞 눌러도로 빠져 라인이 그냥 리고
+한 머리부터
+집어넣 아홉 번째 우승
+제 하지만 20시즌 서머 엔 다시
+한번 부진이 찾아왔고 서였다 클로저
+선수가 선발로 기용되며 벤치에 있는
+시간이 들어갔습니다
+가 길게 싸웠을 때의 강점 그래서
+로가 어 페이커 선수의 빈자리를
+채우는데 부담감이 사실 있었을 것
+같아요 상경 대신 되게 나온 거라
+정말 부담도 많이 됐고 그랬는데 좋은
+모습 보여줄 수 있어 가지고 지금
+되게 좋은 거 같아요 21년도 작년
+월즈 우승에 주역 양대인 감독이
+선임되었습니다 팀의 부진이 계속되자
+사상 최초 쉬인 로스터 돌림판이
+돌아가며 출전 시간도
+오
+예 페이코 위험한 상황에서 아 다시
+들어요 오 이렇게 베이컨을
+끌어줍니다이 시기의 여론은 정말
+최악이었습니다 신인 클로저에 자리를
+양보해야 한다 더 이상 옛날에
+페이커가 아니다든 선넘는 악플과
+비난이 난무했습니다 그렇게 티 1과
+페이커는 최악의 한해를 보내고 있었고
+결국 시즌 도중 양대인 제파 코치진이
+경질되고 못했던 가장 큰 위기를
+맞이합니다 그렇게 코진 경질 이후
+티원은 카오페 국회라는 새로운 조합을
+찾아냈고 겨우 반등에 성공하여 무려
+월드 챔피언십에 진출하는 성과를
+이뤄내대지만 다시 한번 돌리죠 5
+너무 지않 다
+스 와 이거 이거
+끌어다거든 쉽지않네 네 나이스 야
+이기면 된 거야 나이스 대로 갑니다
+제대로 합을 맞춘지 얼마 되지
+않았음에도 당대 최강으로 평가받던
+담원과 사강 명승부를 만들어낸 원과
+페이커 그리고
+부까지 부도 위험해 보이거든요
+그러 계속 는데요 근데 또 살아요
+그리고 마
+마 뭐 괜찮았죠로 안고
+날 야 더블 킬 결국 이렇게 칼까지
+달렸구요 넥서스가 이렇게 파괴됩니다
+오랜 베테랑이자 전설인 페이커와 팩이
+넘치는 신인들로 구성된 새로운 티원은
+다음 시즌을 기대하게 만들었습니다고
+날까지 여기서 정리 당합니다
+결승전으로 간 건 기이 야 정말
+감동이 가득한 오늘 하루 꽉찬
+경기력이었다 계약 기간은 21년도
+아지고 계속해서 발표가 늦어지자
+해외에서 엄청난 오퍼가 들어왔다는
+사실이 밝혀지며 정말 원을 떠나는게
+아니냐는 소문이 있었죠 심지어
+중국에선 240억 제시했다는 사실이
+밝혀지며 해외에서조차 페이커가 이번엔
+정말 이적할 것 같다는 반응이
+많았습니다 하지만 가까스로 재계약에
+성공하며 티원의 남아 우승을 노릴 수
+있게 되었습니다 티원의 주축인만큼
+팀원들을 잘 이끌어서 LCK 세
+시대를 만들어고 하겠습니다 그렇게
+시작된 2022 시즌의 초반엔 많은
+사람들이 우려를 표했습니다 원에 탑을
+책임지던 칸나가 이적하고 유망주였던
+T1 뉴스 출신 제우스를 콜업 아며
+제오 국회라는 새로운 조합으로
+시작했죠 하지만 그런 걱정에도
+불구하고 신인 제우스는 미할
+뛰었고 들어가면서
+어 다 겠는데요 자 그리고 일단
+아래쪽 르겠습니다 달라 폼이 돌아온
+페이커도 신인들과 함께 조화를 이루며
+무려 리그 전승이라는 엄청난 경기력을
+보여줬고 더군다나 플레이오프에서도
+승승장구하며 파이널에 진출했습니다
+전승
+우승으로 도전하는 LCK 예 불사죠
+[음악]
+원 사상 최초로 전승 우승이라는
+대기록을 앞두고 있었죠 그서
+원
+보이는데요 세명 전사
+진격하는데 젠지가 저항해 보지만
+안돼요 어떻게 한 턴만 더 하고
+싶은데 그렇게 강적 젠지를 상대로
+승리하며 전승 우승이라는 엄청난
+기록과과 페이커는
+가
+한번는입니다
+승 이때까지만 해도 대부분의 사람들은
+앞으로 원의 시대가 될 것이라고
+생각했습니다 강이라는 뭔지 야
+겁니다
+그 외 MSI LCK 대표로 출전하며
+팬들을 설레게 만들었죠 지난 워즈에서
+왕이
+돌아왔다라원 전승 우승 때에 폼을
+보여주지 못했고 연달아 실수가 나오며
+홈그라운드에서 렌에게 우승을 내줄
+수밖에 없었습니다 많이 어 이거 안
+돼요 안 돼요 아 초반에는 이거 안
+돼요 만 그 다이
+다 페이 메이커 한번 피해고 아데 마
+뒤에서
+뒤에서데 어 안 갈리나요 안
+갈려요 넥서스 깨면서
+아지
+치 그때부터였을까 페이커와 티원은
+LCK 서머에서 결승전에 진출하긴
+했지만 막상 파이널에선 허무하게
+무너지며 계속 준우승으로
+마감했습니다가 핑퐁이 되는데요 퐁이
+되고 있습니다
+[박수]
+하지만 페이는 포기하지 않고 가장
+중한 드에 완전히 다른
+모습이었습니다
+강 조 페이커와 원을 만나긴 싫다고
+말하기도
+했죠 거의 다 왔어요 진짜 다
+왔습니다 자 거의 봅니다 확실하게 결
+손해게 직전
+전 코 앞에
+있어요가 파괴합니다
+원이 결승전 들어갑니다 그렇게 난적
+진동을 물리치고 올라간 월즈
+[박수]
+[음악]
+결승전 상대는 리그에서 한 번도 저본
+적이 없고 스크림에서 압살했다 알려진
+LCK 4시드
+drx
+습니다만이
+[박수]
+죽 하지만 월 결승전 무대는 역시
+쉽지 않았고 소년만화의 주인공
+렉스에게 패배하며 이번에도 준우승에
+[박수]
+머물렀습니다
+끝이 을 때와 다르게 주변 동생들을
+살피며
+안타까워했고 누구보다 승리를 원했고
+패배의 아쉬움의 감정을 감추지 못했던
+페이커는 어느샌가 동생들을 챙기는
+든든한 마청이 되어 있었습니다 그렇게
+찾아온 또 한 번의 스토브리그
+페이커의 계약은 연장 옵션이 있었지만
+또 한 번 발표가 늦어졌습니다 그렇게
+팬들이 발을 동동구르고 있을 때
+갑자기 들린 희소식 페이커는 원과
+무려 3년이나 재계약 한 원맨을 선한
+것이었습니다 계약기간이 짧은
+프로게이머 특성상 이것은 정말 놀라운
+일이었고 같은 팀인 구마유시 당황했을
+정도였습니다 3년 빡세네 종적으로
+상경 커리어를 따라잡고 싶은 마음이
+있는데 상 3년을으면 안되는데 그렇게
+원의 심장 페이커는 데뷔 10주년을
+맞이했고 올해는 반드시 우승하고
+싶다는로 시즌을
+시작했 아쉽게 승
+놓치니까 는 기분이 그립더라고요 원은
+상대팀이 알고도 당할 수밖에 없는
+팀이라고 생각해요 팀을 맞춰온 원이다
+보니 다시 한번 강해진 모습으로
+스프링 시즌을 시작했고 플레이오프에서
+페이커는 강적 KT 상대로 엄청난
+슈퍼플레이를 통해 승리를
+견인했습니다는 페이 페이커 위치
+페이커고 잡 잡았어요 진짜 마씨가
+때립니다
+했 그리고 아직 은 여이이 자극적인
+다봐야 54분 5분의 경기 넥스가
+결국
+이렇게 페인과 함께 파괴됩니다
+압도적
+[음악]
+1
+아니 하지만 결승전에 티원은 무언가의
+홀린 것처럼
+이상했습니다지
+않았습니다 그렇게 젠지에게 넥서스를
+시한번 준우승을 기록했고
+멤버는 안된다 우승하려고 모인 팀이다
+등 비난이 쏟아졌죠 그때부터였을까
+페이커와 선수들의 멘탈은 나빠질
+수밖에 없었고 끈끈했던 첫 시즌과
+다르게 알 수 없는 불신과 서로간의
+말이 없어지기도
+했죠 아 이이 세스 이렇게습니다 트
+만들어 더구나 2등으로 진출한 MSI
+결승전도 가지 못하고 지에게 패배하며
+3등으로 마감해야
+했습니다 그렇게 시작된 머 시즌 원과
+페이커에게 또 한번 악재가 찾아옵니다
+아 티에 입문 발표가 있었는데요
+페이커 이상혁 선수가 오른팔과 손목
+구위의 통증으로 몇 중간 휴식이
+불가하다 그런 내용이었습니다 다행히
+정민 선수생명이 짧은 프로지만 년이나
+프로생활을 해온 페이커에게 손목
+부상이 찾아온 것이었죠 페이커 이사
+선수의 빠른 회복과 복귀를 기원하면서
+그다 포비가 나옵니다 든든한 마이자
+주장 페이커의 부제는에게는 정말
+실현과 고난이었습니다 페이커가 빠진
+자리를 포비가 채우며 경기에
+출전했지만 엄청나게 떨어진 경기력으로
+부진을 면치 못했고 러도 들고
+있어요네 제스 리아가 비입니다
+동시 그대로
+에이스 전원생 다섯명 다 화 보고
+있습니다 넥서스를 게에서 마무리 치듯
+디렉 시 이번 시즌 페이커가 없는
+티원은 끝이라는 반응들이
+대부분이었습니다 페이커는 아직 완치가
+되지 않았지만 위기에 순간 돌아왔고
+티원은 달라졌습니다서 바론 파워플레이
+5600 6 넘어갈지도 모르겠는데 또
+다시 23분대 23분
+40초 4대 경기를 마무리면서
+아 31일만에 페이카 리하이
+그렇게 구승 구까지 떨어졌던 티원은
+기적적으로 플레이오프에 진출했고 무려
+퍼스트에 빛나는 티를 꺾고 결승으로
+진출합니다에
+광 니다 유신 유신 잘 파랍니다
+케트를 토너먼트에서 죽어버리면서 전해
+그렸듯이
+결승의 진출합니다 와 정말 다양한
+통신사 매치가 있었지만이 마지막
+경기만큼 가장 극적인 경기는 없었던
+거 같습니다 하지만 손목 부상으로
+연습량이 부족했던 페이커의 약점이
+드러났고 연속 준우승이라는 압박감
+때문이었을까대
+일어 결승전에선 또 한번 젠지에게
+무기력하게 대패했고 오연 준우승이라는
+명 아닌 5명을 갖게
+되었죠간에 있는
+거요고
+있습니다 우승 경험 이만은 페이커와
+다르게 동생들은 압박감을 견디기
+힘들었고 멘탈이 강한 구마유시 오연준
+우승이라는 결과를 받아들이기
+힘들었습니다 월즈 또 스프링 MS 머
+이렇게 다섯번에 승을 한 지금은 너무
+우승이 어려워져 버린 거 같아요 저한
+롤드컵 전 인터뷰에서 나머지
+팀원들은이 멤버가 마지막일 수도
+있다는 인터뷰를 하며 현실을 인정하는
+모습이었습니다 이게 반복된 실패 그런
+걸 겪다 보니까 저희가이이 멤버로 할
+수 있는 마지막 대회가 될 수도
+있다고
+생각하는데 이제 승을 못한 한이 기
+때문에 우승을 해야지만 뭔가 해피해피
+하지 않을까 서머가 끝나고 열린
+항저우 아시안 게임에서 국가 대표로
+발탁된 페이커 하지만 서머 시즌
+최강의 폼을 보여주던 쵸비에게 주전
+자리를 내줄 수밖에 없었습니다 항상
+최고의 자리에 있던 그에게 후보가 된
+건 자존심이 상할 수도 있었지만
+페이커는 달랐습니다 수많은 인터뷰에서
+주전으로 출전하는 것보다 팀의 승리가
+우선이라며 뒤에서 묵묵히 동생들을
+지원했습니다 그렇게 금메달을 목에
+걸고 돌아온 페이커는 이제 다른
+목표가 생겼습니다 작년 결승에서
+아쉽게 탈 했기 때문에 더욱 간절했고
+팀원들과 함께 우승의 기쁨을 맛보고
+싶었죠 그렇게 시작된 롤드컵 첫
+경기부터 페이커와 티원은
+흔들렸습니다 옵니다 따라가면서
+사 포 많 뒤로
+넘기면서서고
+뚫는데 결국 이렇게 넥서스가
+파괴가라 겨우 승리하긴 했지만 다음
+상대는 리그에서 천적으로 불리던 우승
+후보
+젠지
+이러면은대 초반 유리한 흐름이었지만
+약간의 실수로 다시 한번 패배할
+수밖에 없었죠 말수도 위험해요지 마
+체로었습니다 캐리아 그리고 봐요 또게
+넥서스의 파괴가 됩니다 하지만
+페이커와 티원은 포기하지 않았고
+자신들이 가장 잘할 수 있는 길을
+선택했습니다 탈출 했는데 페이커가
+같이
+죽여대 그리고 타워 렸습니다이 캐 요
+그래 제도 위 다 잡힙니다 제도 제도
+전사 괴 됩니다 메타가 아닌 자신들이
+잘하는 것을 찾기 시작한 원는 갑자기
+다른 팀이 되어 있었습니다 그렇게
+다음 상대는 MSI 무기력하게
+패배하며 꼭 복수해야 할 팀이었던
+지오가라
+라최 를 상대 압 경기력을 보여주
+강에 진출합니다
+[음악]
+넥넥 근데 상대 자를고 팀 엄
+한드 찾았다며 기대하지 않던 팬들도
+다시금 고개를 들기
+시작했고
+스가
+됩니다 심지어 8강에서 젠지와
+케이티가 모두 탈락하며 원는 마지막
+LCK 희망이 되었습니다 서양
+관계자들은의 압승을 예상하기도 했고
+lpl 강세 속에 부담감을 안고 8강
+매치업을 시작하죠 기형 지금의 저를
+느껴보세요 예아 다시 만나서 반갑다
+최고가 되려면 저를 넘어서야 할
+겁니다 하지만 뚜껑을 열자는 정말
+[박수]
+강했습니다
+후보 로 압도적인 경기력으로 승리를
+따내고
+말았죠이면
+돼 그 타기 시작는
+거죠 대로임을 박살내고
+있고
+이제 남은 상대는 올해 골든 로드를
+노리고 있는 lpl 챔프 징동 페커
+선수는 높은 곳에 올라가려면 늘
+마주해야 하는 벽 같은 존재였어요
+페이커 선수를 꺾고 트로피를 들었을
+때는 세상에 거 다 가진 기분 그들은
+LP 스프링 서머를 모두 차지했고
+LCK 결승에 진출조차 하지 못했던
+MSI 그래도 우승을 차지했던 말
+그대로 우승 후보 1순위 팀이었습니다
+운명 이끄는 대로 최선을 다 하면
+루 선수 잊지 말아야 할 겁니다
+모든길은 결 저를 통합니다 이미 MS
+동 한
+있었 이번 월에서 강를
+상대로 응원하지 않을까 이런 생각이
+또 세삼 들기도 하는데요 그 상대가
+좀 많이 어렵네요 진동 게이밍입니다
+동
+러를 3대으로 제압했던 원이었지만
+동과의 대결은 한치앞을 알 수 없는
+미지수였다 코인토스 마저 동이
+승리했습니다 하지만 징동은 원의 바텀
+듀오를 경계에서 있지 1세트를 내두로
+시작하는데 원을 상대한데 있어서 피와
+같은 주도권 혹은 바텀에서 애쉬
+뿐만이 아니라 정말 다양한 챔피언들이
+정말 다양한 조합으로 위치를 바꿔서
+나올 수 있기 때문에 그런 부분에
+대한 좀 의식을 통해서 징동 게이밍이
+레드로 간 거 아니냐 이런 얘기들이
+많이 나오고 있는데 그렇게 전 세계
+모든 팬들의 주목을 받으며 시작한
+원과 징동의 1세트 바로 한성과
+함께 시작
+하겠습니다 원이 준비한 조커 픽은
+구마유시 리아의 진바 되었습니다
+보통은 아에 밀리 이런식으로 말씀하신
+대로 도합 구성을
+하는데요일까요 확실히 라인전에서
+단점을 보일 수 있는 카드 바텀 어를
+꺼내들었습니다 자 어제도 그런 말씀
+잘 들었습니다만 0% 픽입니다 진동도
+탑인 36가 잘하지 않던 브를 까며
+정면 승부를 펼쳤죠
+준비한으로 보
+깎 이번 시즈 최고의 폼을 보여주는
+너의 한 선을 시작으로 너 선수가
+준비를 굉 잘해왔어요 바텀에서까지
+하면서 바 위 올리는 선을
+냈는데요러 페이의 오리아나
+플레이 는 구마 리아까지
+마지막으로 과성장 제우스가 동을
+유린하며 1세트를 손쉽게
+가져오죠을
+끝
+더 빠 예 그 강한 진동을 24분경
+게임 끝내 버리는데요 전히 제스 칼리
+러면 하지만 징동은 역시 호락호락하지
+않았고 바텀에서 변수를
+만들어내며 그리고
+나서 자 일단 앞라인 밀려갑니다
+마가는데 위 다시 일어날 수 있는데
+말씀대로 마시 정했고요 그리고 넥선
+파괴 기 원점으로 돌립니다
+동 즈는 1대 1이 되었습니다
+러요 돌 러가 이걸고
+있이 세트를 가져온 동이 3세트에서도
+흐름을 잡으며 거의 승기를
+가져갔지만을 뼈
+아해 페이커가
+있었습니다 엄청난 슈토스 한방으로
+하던 흐름을
+시켰고
+가면돼
+지었다 그대로 넥서스를 파괴하며 왜
+자신이 역대 최고의 선수인지 스스로
+증명했죠 동의 핵심이었던 룰러를
+냈습니다 그렇습니다 모든 길는 다를
+통한다 베이커가 길를 막았습니다 른
+팀들의 업다운을 받지만 그래도
+지금까지 나 페니다 게임 내용 정말
+어려웠네 하지만 살아있는 전설이 다시
+한번 진동을 가로 막네요 그렇게
+시리즈의 마무리가 될 수도 있는
+대망의 4세트가
+시작되었습니다 생존이 어렵네요 초반
+카나비 활약 속에 진동이 앞서가는
+듯했으나 렸어요 렸어요
+렸지 렸 살아갈 수가 없을 것
+같면서 일단 잠 하고 다서 나왔요
+페이코의 아지르가 잘큰 카비를
+잡아냈고
+바드 그리고 자르 하고요 옆으로 이동
+어 마시도 그간 천적으로 평가받던
+룰러를 상대로 2대 1 맹활약을
+펼치며 자신을
+증명했습니다 그렇게 페이커는 엄청난
+활약으로 자신이 약속했던 말을 지키며
+lpl 1번 시드인 그들을 중국으로
+돌려보냈습니다
+원
+원 이번 대회였던 페이커의 공약이
+그림같이 실현되는
+순간이었죠 골든로드 저희가
+맡겠습니다 그렇게 징동 마제 아한
+티원은 단숨 우승후보 1순위로 껑충
+뛰어올랐지만 아직 마지막 시련이 남아
+있었습니다
+마지막회를 잘살려서 파이팅해
+상사대 시작전 크게 주을지 못했던
+[음악]
+게이 그들은 군가 많이 닮아
+있었
+웨이는 작에게 엄청난 슬픔과 충격을
+안겨줬던 바로 그를 연상 하는
+[박수]
+팀이었습니다 역사는 되풀이 되는
+것처럼 원과 마주치게 된 것이었죠
+사실 목표로 너무 빠르게 가게 된 거
+같아요 이번에 기회가 없다는 거 잘
+알고 있습니다이 기회를 잘
+살리겠습니다 작년 이맘 때 3대
+0으로의 티원 선수들은 이번 미디어
+데이 땐 완전히 달라진
+모습이었습니다에서 저희가 혼자
+남았다고 해서 부담이 되고나 하진
+않고 저희가 마지막으로 남은 한국
+팀이니만큼 한국 팀의 위상을 지키고
+오겠습니다 작년에 실패를 그냥 넘기지
+않았던 티원 선수들은 결코 방심하지
+않았고 팬들조차 선행을 만들 정도로
+간절한 상황이었습니다 선행이 시작이
+어디서부터 시작된지는 정확히 알지는
+못하지만 팬분들의 그런
+간절함이 많이 느껴져서 저희가 좀 더
+책임감을 가지고 열심히 할 수 있게
+되는 거 같고 그야말로 전세계가
+이들의 거대한 서사의 마리가 어떻
+[박수]
+켜 8강에서 살아남아 lpl 3시를
+리고 결승에
+[박수]
+올라고
+[박수]
+심지어 페이커의 네번째 우승이라는
+대기록과 작년 아쉽게 준우승에
+머물렀던 제국회의 첫 월드컵 우승을
+눈앞에 두고
+[음악]
+[박수]
+있었습니다 반면 웨이보는 얼떨결에
+lpl 희망이 되어 월에서 한번도
+무너뜨리지 못했던 황제 페이커의
+아성을 무너뜨릴 수 있는
+기죠 정신이 번쩍들게
+해줄게 그렇게 다시 한번 결승에
+진출한과 페이커 마지막을 앞둔
+페이커의 가구는 달랐습니다 세번
+우승은 저자신을 위한 거였습니다 네번
+우승은
+[음악]
+을위한니다 자신이 아닌 팀을 위한
+승리를 간절하게 원했고 그렇게
+결승전이
+시작되었습니다 우승을 눈앞에둔 마지막
+3세트에서 마치 과거 월주 우승
+때처럼 환상적인 플레이를 보여주며
+상대 를 압도했고 방에서
+방 갔다 왔다갔다 왔다갔다 그리고
+이거 과거 월주 우승 때처럼 환상적인
+플레이를 보여주며 상대의 웨이보를
+압도했고
+안되는데요
+공대 그렇게 7년 만에 다시 한번
+즈에서 우승컵을 들어올릴 수
+있었습니다 원의 네번째 우승이 와
+제우스 오더 구마 리아의 첫 번째
+월즈 운이
+이형교인 고맙습니다 과거 패배의
+슬픔에 뜨거운 눈물을 흘리던 페이커는
+어느새 동생들의 눈물을 위로하고
+챙기는 든든한 마성이 되어 있었고
+이제는 동생들과 함께 기쁨의 미소를
+지으며 자신의 10주년을 완벽하게
+장식했습니다네 안녕하세요 저는 원의
+프로게이머 페이커 이사입니다 정말
+멋진 경기 패쳐 준 SKT 테도 그죠
+승희 승희의 이런 어가 있으면 아
+페이커의 저는 아 겠죠 수 있다한테
+판는 깔렸다 모두 팀을 외친다 왔다
+왔다 잘해보자
+렉스가이 말도 안되는 스토리를
+완성시킵니다 아이다 얘들아 했 했다
+같이 같은 꿈을 던 선수들도 많거든요
+바를 떨고 있는 캐리아 정말
+잘했습니다네 번째 우승을 노리고 있는
+고투 페이커 절대로 우승을 놓치지
+않을 겁니다
+네번째 우승은 네번째 우승은 네번째
+우승은 우리 팀을 위한 것 팀을
+[박수]
+위한
+재을 합니다 페이커는 더 이상 말이
+필요 없을 정도로 리그 오브 레전드의
+전설입니다를
+막습니다 다운을 받지만 그래도
+지금까지 나아 있 트럼프 이겁니다
+메이저 국제 대회 최다 우승 월즈
+단독 최다 사회 우승 월즈 최초 2회
+연속 우승 MSI 최초 2회 연속
+우승 LCK 최다 10회 우승
+국가대표 금메달 라이어 주관 모든
+국제 대회에서 우승한 최초이 선수등
+화려한 경력은 차치하더라도 10년에
+세월 동안 논란이 없을 정도의
+프로의식 항상 팬들께 감사하는 마음
+등 명실 상고한 리그 오브 레전드
+역사상 최고의 선수이자 보트입니다
+너무 오랜만에 우승한 거 같아서 저도
+시간이 잘 안 나는데 그동안 너무
+많이 응원해 주셔서 감사드리고
+앞으로도 팬분들을 위해서 열심히</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025 페이커 아타칸상륙작전ㄷㄷㄷ</t>
+          <t>"이것" 켜져 있으면 내 계좌, 개인정보 전부 빠져 나갑니다. 휴대폰 이 설정 지금 반드시 꺼주세요!</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RNL386HwezM</t>
+          <t>https://www.youtube.com/watch?v=TKOQi-Gj2Es</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>숭배하라</t>
+          <t>시니어 정보탐정</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UChT_3672e3gi9TzLUCpvDow</t>
+          <t>https://www.youtube.com/channel/UC2eaFkMQMgOXcNfFsRN64Mg</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>501570</t>
+          <t>3,334,598</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>35600</t>
+          <t>133,000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2025-08-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>2025-06-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>스마트폰 설정 하나 때문에 내 계좌,
+사진, 위치 정보까지 고스란이 털릴
+수 있습니다. 근데요. 그걸 막아주는
+기능 폰 안에 다 들어 있습니다.
+문제는 어디 숨어 있는지 아무도
+정확히 알려 주지 않는 거죠. 그래서
+오늘은 삼성폰 사용자라면 꼭 꺼야 할
+일곱 가지 설정 어디서 찾고 어떻게
+바꾸는지 요점만 딱 집어서 알려
+드릴게요. 지금 시작하겠습니다.
+첫 번째 설정은 평소에 자주 쓰면서
+무신코 지나쳤던 부분입니다. 문자나
+카톡으로 집 주소나 통장 계좌번호
+복사해서 붙여 넣기 해 보신 적
+있으시죠? 근데요. 복사한 내용 그냥
+사라질까요? 그렇지 않습니다. 우리가
+문자나 카톡에서 복사하면 그 내용은
+클립보드라는 곳에 임시로 보관됩니다.
+평소에 카카오 톡을 많이 쓰니까
+여기서 보여 드릴게요. 카톡을 열어서
+메시지를 입력하고 꾹 눌러서 복사를
+해 보세요. 클립보드에 복사했어요.
+이런 안내 뜻이죠.
+그다음에 빈 입력창을 누르면 방금
+복사한 내용이 아래에 딱 뜹니다.
+옆에 X 표시를 눌러 주세요. 그러면
+아래쪽에 아이콘이 여러 개 뜨는데
+이걸 도구모음이라고 부릅니다.이
+중에서네 번째 네모 모양 아이콘
+보이시죠? 이게 바로 클립보드입니다.
+한번 눌러 볼게요. 맨 앞에는요.
+방금 복사한 내용이 저장돼 있습니다.
+그리고 그 뒤로 예전에 복사했던
+주소나 카드 번호, 연락처 같은
+정보들이 남아 있어요. 저도 모르게
+여기 쌓여 있었어요. 자, 그런데
+문제는 악성에 비 클립보드에 접근해서
+카드 번호나 비밀 번호 같은 걸 몰래
+빼갈 수 있다는 건데요. 클립보드를
+통한 정보 유출은 실제 보안 사고의
+주요 원인이에요. 그러니까 이제 당장
+해야 할 일은 바로 클립보드 안에
+들어 있는 정보를 깨끗하게 지어 주는
+겁니다. 이번엔 문자 메시지 앱을
+열어 주세요. 방법은 카톡이랑
+똑같습니다. 빈 입력창을 누르고
+아래쪽에 도구 모음이 뜨면네
+번째 클립보드 아이콘을 눌러 주세요.
+방금 전 카카오 톡에서 본 내용들
+똑같이 들어 있습니다. 여기서 삭제할
+항목을 꾹 누르고 위에 보이는 휴지통
+아이콘을 눌러 주세요. 이렇게 하면
+바로 지어집니다.
+참고로 카톡이든 문자든 클립보드는
+하나로 연결되어 있으니까 한 군데서만
+지우시면 됩니다. 다 지우셨다면
+그다음 알림 설정까지 해 두셔야 진짜
+안심됩니다. 이건 수상한 앱이
+클립보드에 접근할 때 바로 알려주는
+보안 기능이에요. 휴대폰 화면을
+위에서 아래로 쓸어내리고 설정
+톱니바퀴 모양 아이콘을 눌러 주세요.
+여기서 보안 및 개인 정보 보호
+항목을 찾아서 그 안에 있는 제어 및
+알림을 눌러 주세요. 그다음 클립보드
+접근시 알림 항목을 파란색 켜짐
+상태로 바꿔 주세요. 이렇게 해
+두시면요. 클립보드에 다른 앱이
+접근할 때 알림이 뜨니까 수상한 건
+바로 차단하실 수 있습니다. 자,
+그런데요. 지금까지 말씀드린
+클립보드보다 더 무서운게 하나
+있습니다. 바로 우리가 직접 찍은
+사진입니다. 혹시 이런 적
+있으신가요? 여행 가서 사진 한 장
+찍어 보냈더니 상대방이 여기 어디네요
+하고 바로 마치는 거예요. 우리도
+한번 해 볼까요? 카카오 톡으로
+친구에게 받은 여행 사진 정확한 위치
+맞춰 볼게요. 저장한 사진을
+갤러리에서 확인해 볼게요. 사진 찍은
+날짜는 물론이고 위치까지지도 위에
+자세하게 표시되어 있습니다. 놀랍게도
+요즘 스마트폰은 사진을 찍을 때
+촬영한 위치의 GPS가 자동으로 같이
+저장됩니다.이 이 기능을 위치
+태그라고 하는데요. 갤럭시 휴대폰은
+대부분 켜져 있을 겁니다. 예를 들면
+집 앞에서 손주 사진을 찍어서 가족
+단톡방에 보냈다고 해 볼게요. 근데
+그 사진이 다른 사람한테 또
+전달되거나
+카카오 앨범 같은데 올라가면 어떻게
+될까요? 내가 모르는 사이에 우리지
+위치가 남에게 노출되는 상황이 생길
+수도 있습니다. 그래서 지금부터
+사진에 내 정보 위치가 남지 않도록
+딱 꺼두는 방법 알려 드릴게요.
+스마트폰에서
+카메라 앱을 열어 주세요. 왼쪽 위에
+톱니바퀴 모양 보이시나요?
+혹시 안 보이시면 저처럼 아래쪽에
+점개의 버튼을 눌러 보시면 그 안에
+톱니바퀴 설정이 숨어 있을 수
+있어요. 설정을 누르시면 위치
+태그라는 항목이 나옵니다. 이걸
+회색으로 꺼 주세요. 그럼 앞으로
+새로 찍는 사진에는 위치 정보가
+따라붙지 않습니다. 그럼 이미 찍은
+사진은 어떻게 하냐고요? 간단한 방법
+하나 알려 드릴게요. 카카오토 나와의
+채팅방에서
+사진을 한번 보내 보세요. 이때
+보내는 사진의 화질은 원본이 아닌
+일반 화질로 설정해 주세요. 그다음
+거기서 다시 사진을 저장해 보세요.
+이렇게 하면 위치 정보가 싹 지워진
+사진으로 새로 저장됩니다. 이거 꼭
+확인하시고 불필요한 위치 정보는
+깔끔하게 지워 주세요. 자, 그리고
+이번엔 많은 분들이 경험하셨을
+상황인데요. 혹시 휴대폰이 내
+이야기를 엿듣는 것 같은 적
+없으셨나요? 오전에 친구랑 통화 중에
+무신코 했던 얘기가 있는데 그날
+오후부터 네이버나 유튜브나 그 광고만
+계속 뜨는 거예요. 사실 우리 대화를
+엿듣는 건 아니고요. 내 스마트폰에
+광고 아이디가 있기 때문에 벌어진
+일입니다.이 광고 아이디라는게
+뭐냐면요. 쉽게 말해서 광고 회사들이
+우리 폰에 붙여 놓은 이름표 같은
+거예요.이 이표에 내 검색 기록과
+사용 패턴이 다 기록되는데 이걸
+보고서 아이 사람한테 이게 먹히겠구나
+싶은 광고를 붙여서 들이미는 거예요.
+그래서 광고 아이디는 꼭 삭제해
+주셔야지 나를 노리는 맞춤형 광고의
+표적에서 피할 수 있습니다. 광고
+설정은 좀 숨겨져 있으니까 이번엔
+검색으로 찾아볼게요. 먼저 스마트폰
+화면을 위에서 아래로 쓸어내리고
+위쪽에 보이는 톱니바퀴 모양의 설정
+버튼을 눌러 주세요. 화면 오른쪽
+위에 돋기 보이시죠? 그걸 눌러서
+광고라고 검색해 보세요. 그럼 광고
+관련 설정들이 보일 텐데요. 보안 및
+개인 정보 보호 또는 개인 정보이라는
+메뉴에 있는 광고를 눌러 주세요. 그
+안에 들어가서 쭉 내리면 광고라는
+항목이 또 나옵니다. 이걸 눌러
+주세요. 여기서 광고 아이디 삭제라는
+버튼이 보이면 그걸 눌러 주세요.
+그럼 바로 이름표가 제거되는 겁니다.
+혹시 아이디 삭제가 없으면 광고
+아이디 재설정이나
+맞춤 광고 제한 항목이 있을 거예요.
+그걸 선택하시면 됩니다. 나를
+따라다니는 찜찜한 광고 노출을 확실히
+줄일 수 있습니다. 이제 다음 단계로
+넘어가 보겠습니다. 지금부터는 정말
+강력한 보안 방어막 세트입니다. 요즘
+택배 문자, 부고 문자 안에 숨어
+있는 링크 한번 잘못 누르는 순간
+나도 몰래 가짜비 깔려 버린다는 얘기
+많이 들어 보셨죠? 그때부터는요. 내
+스마트폰 안에 있는 정보들이 그대로
+털릴 수 있습니다. 아차 실수 한
+번으로 누구나 겪을 수 있는
+일입니다. 그래서 지금 알려 드릴이
+설정들 꼭 미리 배워 두셔야 합니다.
+자, 먼저 실수록 문자 속 링크를
+누르지 않도록 미리 차단해 둘 수
+있습니다. 메시지 앱을 열어 주세요.
+오른쪽 위에 점 세 개 누르시고
+맨 아래 설정으로 들어가 주세요.
+거기서 추가을 누르면 연락처에서 보낸
+웹 링크 미리 보기와 링크 열기
+허용이 두 가지 항목이 보이실
+거예요. 이걸 둘 다 파란색이 아닌
+회색으로 꺼 두세요. 이렇게만 해
+두시면 문자 속 링크를 실수로 눌러도
+바로 열리지 않습니다. 진짜 연결할
+거냐고 한 번 더 물어봐 주니까
+그나마 한 숨 돌릴 수 있어요.
+그런데요. 애초에 그런 위험한 문자가
+오지 않게 막는 방법도 있습니다.
+방금 전과 똑같이 메시지 앱에서 점
+세 개 누르시고 설정 들어가신 다음에
+이번엔 스팸 및 차단 번호 관리로가
+주세요. 여기 보시면 악성 메시지
+차단이라는 메뉴가 있습니다. 이건
+회색이면 꺼진 상태입니다. 반드시
+파란색 사용 중으로 바꿔 주세요.이
+이 기능은 경찰청 같은 정부에서
+분류한 악성 번호를 자동으로 차단해
+주는 기능입니다. 무조건 켜 두셔야
+합니다. 자, 마지막입니다. 문자든
+링크든 상관없이 이상한 앱이 깔리는
+걸 아예 차단하는 기능입니다. 먼저
+스마트폰 소프트웨어가 최신인
+분들은요. 정말 강력한 기능이 새로
+생겼습니다. 아까처럼 스마트폰의
+설정에 들어가셔서 아래쪽에 보안 및
+개인 정보 보호로 들어가 보세요.
+여기에 보안 위험 자동 차단이라는
+메뉴가 있습니다. 이걸 눌러서 파란색
+사용 중으로 바꿔 주세요. 이렇게
+하면 스미싱 문자가 오든 링크를
+누르든 말든 모든 악성앱 설치를
+자동으로 막아 줍니다. 게다가 충전기
+연결했을 때나 컴퓨터 연결했을 때
+몰래 깔리는 악성 코드까지
+막아줍니다. 이건 정말 보안 백신
+같은 겁니다. 삼성에서 작정하고 새로
+만든 보안 기능이에요. 이건 안 쓰면
+정말 손해예요. 혹시 아직 업데이트
+안 된 기기라도 괜찮습니다. 휴대폰
+설정에서 보안 및 개인 정보 보호를
+선택하고 그다음 기타 보안 설정으로
+들어가 주세요. 거기서 출처를 알 수
+없는 앱 설치 항목으로 들어가서 모두
+허용 안함으로 바꿔 주시면 됩니다.
+이렇게 하면 공식 앱 스토어에서 받은
+앱은 정상적으로 설치가 되지만 가짜
+앱은 절대로 깔리지 않습니다. 꼭
+필요한 경우에는 잠깐만 허용했다가
+바로 끄면 되니까요. 이거 하나만 해
+두시면 내 휴대폰에 이상한 앱이 몰래
+깔릴 걱정은 이제 안 하셔도 됩니다.
+다 됐습니다. 여기까지 따라오신
+분들은요. 스마트폰 지키는데 꼭
+필요한 설정들 제대로 챙기시는
+겁니다. 오늘 알려 드린 일곱 가지
+중에서요. 꼭 전부가 아니어도
+괜찮습니다. 한두 가지만 잘해 두셔도
+이전과는 비교도 안 될만큼
+든든해집니다. 오늘 보신 내용 중에
+이건 우리 가족도 꼭 알았으면 좋겠다
+싶은 설정 있으시면 주변분께도 알려
+주세요. 설명이 어렵다면이 영상을
+공유해 주셔도 좋습니다. 그리고 난이
+설정이 제일 중요하다 생각드신 거
+댓글에 한 줄 남겨 주시면 다른
+분들께도 도움이 될 거예요. 그리고
+좋아요, 구독, 알람 설정까지 눌러
+주시면 영상 만드는데 큰 힘이
+됩니다. 앞으로도 꼭 필요한데 잘
+몰랐던 스마트폰 정보들 쉽고 친절하게
+알려 드리겠습니다. 오늘도 건강한
+하루 보내시고 다음 영상에서 또
+뵙겠습니다. 하겠습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>손흥민보다 높은 연봉?, 프로게이머 페이커의 놀라운 사실 3가지</t>
+          <t>플레이가 너무 아쉬운 리신을 만난 페이커</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=WgevBgYEfpU</t>
+          <t>https://www.youtube.com/watch?v=YUGhUmRBs58</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>인물쇼츠팅</t>
+          <t>롤 GOAT</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCCrcK1uw1JyOu0ni7virg7A</t>
+          <t>https://www.youtube.com/channel/UCeAQdTFkwBk47nsau_5VkDw</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>10583075</t>
+          <t>595,378</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>63500</t>
+          <t>1,830</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2023-11-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>2025-07-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>CS 안 먹고 그냥 상대가 죽어주기
+기다리는 스타일이구나. 언제까지 안
+먹나 한번 볼게요.
+&gt;&gt; 바텀에서
+&gt;&gt; 우리 정글이 죽었는데 알리스타가
+미드다. 이건 뭐죠? 얼마나 못한
+거야? 이팀
+[음악]
+빠졌잖아. 왜 거기 백 백무빙을
+처리시나?
+왜 안 날아가? 와, 너무 못해.
+[음악]
+&gt;&gt; 와, 난 이건 너무 짜증난다. 리신이
+노스프레인데. 근데이 사람 뭐야?
+도대체 말을 아끼겠습니다.
+[음악]</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>페이커가 인정한 아이돌</t>
+          <t>한화전이 끝나고 곧바로 솔랭 돌린 오너 케리아 페이커..</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=u29cOo8LgAo</t>
+          <t>https://www.youtube.com/watch?v=2qFrKRqK3BA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>esports KBS</t>
+          <t>숭배하라</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UC9_093tAK3bXyZfT84efbvg</t>
+          <t>https://www.youtube.com/channel/UChT_3672e3gi9TzLUCpvDow</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1938223</t>
+          <t>653,946</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>576000</t>
+          <t>36,200</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2025-01-10 00:00:00</t>
+          <t>2025-09-14 00:00:00</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -1127,189 +3240,262 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>페이커 4년 재계약 최대 피해자</t>
+          <t>페이커 흐웨이의 제드 완벽상대법 ㄷㄷ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=K7XJP_hJNZw</t>
+          <t>https://www.youtube.com/watch?v=IxxgGOlR1YY</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>롤민녀</t>
+          <t>롤냥이</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCVxQ3kdXJd7H53m1E_F8Axg</t>
+          <t>https://www.youtube.com/channel/UCFFtfAeEOt72mhYe8xTk5qA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1518842</t>
+          <t>4,489,976</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>1,530</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2025-07-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>2025-04-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>페이커의 제도 완벽 상대법 끼를 못
+맞춰
+줍니다. 이번에 맞춰 줄게요.를
+찍어서 이렇게
+맞춰주고요. CS 차이를 버려
+[음악]
+줄게요. 피스를 안 해줍니다. 잘
+됐기 때문에
+창을 왼쪽으로 쓸
+[음악]
+거거든요. 이거 아직
+[음악]
+네. 한번
+빼주세요. 한번 빼주고 안나 좀
+빠졌는데 상관없죠.
+피해주고요.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>페이커의 텔포판단이 이해안가는 칸 ㅋㅋㅋ</t>
+          <t>페이커의 신전</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9aUu4r4S_ZA</t>
+          <t>https://www.youtube.com/watch?v=GRxvIRJsMLY</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>롤박스</t>
+          <t>5가지</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCFT0hhFLDWMac4XKR9Qe_Sw</t>
+          <t>https://www.youtube.com/channel/UC4YE-r3O9mcddaUTgBO1pqA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>684074</t>
+          <t>1,546,836</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>94,500</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2025-08-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>2025-01-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>직접 설계한 사랑의 집이랍니다 최근
+페이커가 집에서 팀원들에게 파스타를
+만들어 주는 영상이 공개되면서
+페이커의 집이 또다시 화제가 되었는데
+궁전 아니 신전이라 불리는 페이커의
+집에 대해 알아보겠습니다 대리석
+베이스의 높은 친구를 통째로 쓰는 한
+층은 오로지 페이커의 역사와 팬
+선물로 전시되는 것을 시작으로 나머지
+공간을 살려 다섯 명의 팀 게임을 할
+수 있는 pc 룸 리클라이너가 설치된
+무비룸 실내에서 스포츠를 즐길 수
+있는 스크린 골프와 당구대가 있는데
+쉬는 시간이 없고 너무나 바쁜 아들
+페이커와 팀원들이 언제라도 와서 즐겁
+게 마음껏 쉬고 가라고 혼축 설계에
+능통하신 페이커의 아버지가</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>7명의 프로가 말하는 페이커</t>
+          <t>페이커한테 패드립?</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=TwdYJrU1qc0</t>
+          <t>https://www.youtube.com/watch?v=G7S3TPW9JY8</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>롤한입</t>
+          <t>5가지</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UC6ZeliIDAOqjz5u-_1g0iRg</t>
+          <t>https://www.youtube.com/channel/UC4YE-r3O9mcddaUTgBO1pqA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>104353</t>
+          <t>2,656,121</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>94,500</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>2024-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>페이커가 롤토체스를 하는데 드립을
+당합니다 머거 해야 될 것 같데 거랑
+뭐야
+라상
+[음악]
+라싸 상대방이 나 칭찬하고 있어 근데
+[음악]
+안오면 근데 못하긴 해 이거 야 우리
+다 같이 부르면 오긴 해
+미이 아니잖아 어 지금 빨리 보내야
+되고 아 빨리 보내 봐</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>페이커: 건방진 클라이드 #페이커 #t1</t>
+          <t>T1 롤드컵 결승전 마지막 순간 팀보이스</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8NhLOS6wCm4</t>
+          <t>https://www.youtube.com/watch?v=Nqe2GJNRYyw</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>티원숭배</t>
+          <t>아카캉</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UC2nMvHgHEybcEb36TPhACzw</t>
+          <t>https://www.youtube.com/channel/UClK-4_77WOTHBArekj-WRpA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>15591</t>
+          <t>2,406,746</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>3710</t>
+          <t>381,000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>2024-11-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>가줄게 가줄게 외야게 뛰어보자 그럼
+탑
+뛰어보자 끊어줄게 끊어줄게 아리 텔
+못가 텔 못가 텔 못가 아리 못가
+아리 못가 아래 없어 거기 빠지면서
+와야 돼 거기 아래 없어 아 없어 아
+없어 야 시야 시 오 좋 좋 일 왼
+왼왼 맞아 맞아 어 살아볼래 좋은데
+좋데 데리 없어 리 없어 잭스 맞 스
+스 잭스 잭스 스 스 잭스 스 잘봐
+잘 끝났냐 이거 나이스 끝나 탑탑 탑
+이거 점사 잘하면 끝날 것 같은데
+해봐이 잘했 해봐 해봐 레 내가 크
+카 거의 끝나거든 이거 아 해보자
+보자 해보자 해보자
+[웃음]
+[음악]</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>페이커 조각상 공개</t>
+          <t>롤드컵 결승 페이커 하이라이트 해외 해설 #페이커 #leagueoflegends</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Kk1k411XCoc</t>
+          <t>https://www.youtube.com/watch?v=105YX7hWSAs</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>롤한입</t>
+          <t>롤해외반응</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UC6ZeliIDAOqjz5u-_1g0iRg</t>
+          <t>https://www.youtube.com/channel/UCrzyG49_fA0rX08FY8aOxUQ</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>71433</t>
+          <t>424,990</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>394</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2025-09-05 00:00:00</t>
+          <t>2024-11-02 00:00:00</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -1317,75 +3503,100 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>드디어 공개된 페이커 올프로 투표 내역ㄷㄷ</t>
+          <t>페이커에게 롤 알려주시는 롤잘알 할머니 #유퀴즈온더블럭</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pXqSgMOfntU</t>
+          <t>https://www.youtube.com/watch?v=AesvqCszK6Y</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>숭배하라</t>
+          <t>tvN D ENT</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UChT_3672e3gi9TzLUCpvDow</t>
+          <t>https://www.youtube.com/channel/UCsRIHt5FkbGc6cQtCxt-ufA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>544020</t>
+          <t>117,715</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>35600</t>
+          <t>5,220,000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2025-09-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>2023-12-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>카톡으로 장문의 문자 보내시고 아니
+그 할머니께서 실제로도 뭐 게임을
+워낙에 많이 보시고 응원하시고 그
+이게 이제 선수 못지 않게 좀 이쪽
+관련 지식이 되게 많으시다 그래요
+아시는게 그래서 어 한번은 게임하는
+걸 보시고 어 오리아나로 6 레벨만
+되면은 충격파로 폭탄을 날릴 텐데
+이런 훈수를 두셨다고 이거 저희는
+지금 뭔 얘긴가 자 한 번만 더
+오리아나로 6 레벨만 되면은 충격파로
+폭탄을 날려버릴 텐데네 뭐게 게임
+용어인데 예예
+오 6레벨 되면 충격파 쓴다는 말
+6레벨이 돼야 이게 충격파를 쓸 수
+있는 거예요네 맞아요 아 처음에 우리
+하나로 아홉개 먹었지 일다 킬 먹고
+왜 킬
+먹었잖아요 경하게 악 말고 자게
+들어가는게 그게 좀 그런데
+피 딴사람이
+먹으면지</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>마린이 말하는 다른 선수들과 페이커의 다른 점</t>
+          <t>페이커 반응속도 레전드..</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5UD9mvsJa8E</t>
+          <t>https://www.youtube.com/watch?v=8a9tklJqS2c</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>포로롤</t>
+          <t>편집하는 고로상</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCicad9pMG7HSg_JXqK0Mjqg</t>
+          <t>https://www.youtube.com/channel/UC7lRvU_VthCCfydkLVqPTOg</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1854180</t>
+          <t>11,516,334</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>5,310</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2025-02-08 00:00:00</t>
+          <t>2022-04-09 00:00:00</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -1393,151 +3604,214 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>페이커 때문에 서울대 의대생들이 분노했던 사건</t>
+          <t>결승전 5세트 페이커의 갈리오를 본 우지 반응</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_BEX599uVqA</t>
+          <t>https://www.youtube.com/watch?v=34jZ3XGfsdo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>롤카월드</t>
+          <t>롤대남</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCkxeE1hSP2ckoCVYy_8wSCg</t>
+          <t>https://www.youtube.com/channel/UCYhkWfrxKgScIlOmzFrk3Ng</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1472234</t>
+          <t>771,362</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>37100</t>
+          <t>71,600</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2025-08-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+          <t>2024-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>lpl LCK 이길 수 있나요 내가
+절대 용납 못함 가오 세트는 온누리
+상품권이 필요할 때마다 잘리고 스턴
+못 맞춤 크크 오피셜 월지 결승 단
+한 번도 깨지지 않은 징크스 빨
+차이니즈 캔고 원는 lpn게지지
+않습니다 김동아 선생님 보고 계십니까
+갈리오 박치기우지 반응 맞도리네 크크
+내 기억상으론 갈리오 짜증 나서가
+아니라 엘크 플 있는데 뭐 하는
+거냐고 했던 걸로 기억 근데 반응은
+찰자 저거 카이사 뻘플 쓴 거 덕분에
+탑 교전해이긴 크크 풀 있었으면
+갈리오 큐 피하고 팀원 오기 전에
+그라 갈리오 다 뒤졌을 듯 연간의
+피해자 미움받을 용기를 가진 자와
+그러지 못한 자 그렇게 잘 큰
+아리조차도 3코어로 조야 올리는데
+미드 갈리오로 데케 올려버리는 대상형
+아리로 조약 가는 건 캐리 안
+하겠다는 거지 페이커 있으면 리치베인
+올렸다 시원이 승기 잡으니까 그제서야
+옷버서서 유니폼 보여준 크크크
+크크크크 바론 침과 동시에 벗기
+시작하네 왜 홈메이드 에디션 아님
+한겹 터 벗으면 안에 blg 있는 거
+아니야 T1 월즈 역사상 가장
+힘들었던 lpl 팀 17 아지와 2
+3 진동을 제치고 이사 blg 최고의
+상대로 등급 다시 부터도 솔직히
+모른다</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>T1 화내는 도란 놀리는 페이커 ㅋㅋㅋㅋ #도란 #페이커</t>
+          <t>SKT T1 벽느낀 사람</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=hL4NBUwg5SU</t>
+          <t>https://www.youtube.com/watch?v=7wgHF3CiB6U</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>롤컷</t>
+          <t>프레이 TV</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCx_ObjBWhwt11FeRI0PrESA</t>
+          <t>https://www.youtube.com/channel/UCSzHok6X5qXEO7cjvVnE62g</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>635597</t>
+          <t>3,347,298</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>4550</t>
+          <t>667,000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2025-08-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>2024-06-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>준식이 낮은 입단 테스트 왔을 때는
+약간 인정할게 병 느낄 정도로 두드
+페긴 했을 텐데 그 그땐 근데 나
+존나 미친 놈이긴 했어 그때 진짜
+어나더 있어 그때 그랬을 거예요 그때
+무슨 구도를 했어도 다 이겼어 가지고
+그때 그때는 좀 잘했지 뭐 그런
+준식이 SKT 가서 한 판을 못
+[음악]
+[웃음]
+겠더라 잘하더라</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>페이커가 생각하는 자신보다 뛰어난 미드ㄷㄷ</t>
+          <t>페이커 VS 제드99</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xWM3u0VnOAk</t>
+          <t>https://www.youtube.com/watch?v=BDdd_n7luX0</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>숭배하라</t>
+          <t>5가지</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UChT_3672e3gi9TzLUCpvDow</t>
+          <t>https://www.youtube.com/channel/UC4YE-r3O9mcddaUTgBO1pqA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>955213</t>
+          <t>1,201,940</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>35600</t>
+          <t>94,500</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2025-07-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>2024-06-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>페이커 이즈 리얼인데 제드장인 제드
+구구와 미드에서
+[음악]
+[음악]
+[박수]
+[음악]
+만났습니다 히어
+[박수]
+평화가
+[음악]
+함께하게 집중하
+[음악]</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>국가권력급 페이커 요네</t>
+          <t>한화전 끝나자마지 솔랭돌린 페이커 ㄷㄷㄷ</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8L9eMYZWV2U</t>
+          <t>https://www.youtube.com/watch?v=wPXnXi8uCE0</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>T1 Faker</t>
+          <t>롤박스</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCpJw2H9KKqwCCGQKRh1Bf2w</t>
+          <t>https://www.youtube.com/channel/UCFT0hhFLDWMac4XKR9Qe_Sw</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1637081</t>
+          <t>99,703</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2050000</t>
+          <t>2,020</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2024-01-29 00:00:00</t>
+          <t>2025-09-14 00:00:00</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -1545,78 +3819,100 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>'페이커가 필사적으로' 웃참했던 순간들</t>
+          <t>이거 진짜 찾기 어렵습니다 갤럭시워치 설정 #shorts</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BAjeFvzgl60</t>
+          <t>https://www.youtube.com/watch?v=wuVJguofcWU</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>롤따봉</t>
+          <t>팁톡, 쉽게 알려주는 꿀팁</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCoo2pYADRxbV0q4LRrF4yNg</t>
+          <t>https://www.youtube.com/channel/UCP7eGwvW1iDQwNhnIrPVwGg</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>860359</t>
+          <t>132,153</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>9800</t>
+          <t>107</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2025-05-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>2024-08-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>아니 이게 왜 안
+[음악]
+눌러져 이렇게 위에서 아래로 제스
+하고 설정 버튼 누른 다음에 쭉
+내려서 배터리 및 디바이스 케어
+여기서 다 절전 모드 해제 찾아보는데
+배터리 잔량 나오는 화면 한 번만 더
+눌러 주시면 절전 모드 해제가
+나옵니다 이거 찾다가 빡 쳐서
+올렸습니다</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3년만에 다시 돌아온 페이커의 손캠</t>
+          <t>페이커와 오너를 화나게 한 얼불춤 #t1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ArSOVX0qQQA</t>
+          <t>https://www.youtube.com/watch?v=B-UlIAHcIho</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>T1 Faker</t>
+          <t>역천괴케리아</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCpJw2H9KKqwCCGQKRh1Bf2w</t>
+          <t>https://www.youtube.com/channel/UCylPlgEk5g4Vwt8dMADsM7A</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>286446</t>
+          <t>28,322</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2050000</t>
+          <t>3,840</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2025-08-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>2023-04-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>여기 좀 치워봐
+아 이거 좀 채워보라고 아 이번엔
+빠르다고 어떡해
+뭘
+빨라
+천천히 했는데</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
